--- a/AppFiles/4mforms/BIPH4M-2608-005_D311-004_V1.01工程変更申請書__Manufacturing Process Change Request 1.xlsx
+++ b/AppFiles/4mforms/BIPH4M-2608-005_D311-004_V1.01工程変更申請書__Manufacturing Process Change Request 1.xlsx
@@ -13,11 +13,11 @@
     <sheet name="JPN_VINA" sheetId="15" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'JPN_ENG '!$A$1:$T$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">JPN_CHN!$A$1:$T$49</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'JPN_ENG '!$A$1:$T$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">JPN_VINA!$B$1:$T$49</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,46 +38,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t xml:space="preserve">     </t>
   </si>
   <si>
     <t>No.</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>工程変更申請書</t>
-    <rPh sb="0" eb="2">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>責任者</t>
   </si>
   <si>
     <t>担 当</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <t>MANUFACTURING  PROCESS  CHANGE REQUEST</t>
-    <phoneticPr fontId="41"/>
+    <t xml:space="preserve">MANUFACTURING  PROCESS  CHANGE REQUEST</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>Approve</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="ＭＳ Ｐ明朝"/>
@@ -86,41 +70,32 @@
       </rPr>
       <t>ｄ</t>
     </r>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>PIC.</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>会社名</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>年・月・日</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Company</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>yy/mm/dd</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>部品コード</t>
-    <rPh sb="0" eb="2">
-      <t>ブヒン</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve">部品名
 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Times New Roman"/>
@@ -128,20 +103,19 @@
       </rPr>
       <t>Part name</t>
     </r>
-    <rPh sb="0" eb="2">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="0" eb="2">
       <t>ブヒン</t>
     </rPh>
-    <rPh sb="2" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="2" eb="3">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>Part Code</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -150,7 +124,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="MS PGothic"/>
@@ -158,7 +132,7 @@
       </rPr>
       <t>変更内容、変更理由</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -167,7 +141,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
@@ -175,25 +149,25 @@
       </rPr>
       <t>Change content &amp; Reason</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="3" eb="5">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="3" eb="5">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="6" eb="8">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="8" eb="10">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="8" eb="10">
       <t>リユウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> BTSL </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -202,7 +176,7 @@
       </rPr>
       <t>変化点確認表</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Times New Roman"/>
@@ -210,25 +184,25 @@
       </rPr>
       <t>No.</t>
     </r>
-    <rPh sb="6" eb="8">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="6" eb="8">
       <t>ヘンカ</t>
     </rPh>
-    <rPh sb="8" eb="9">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="8" eb="9">
       <t>テン</t>
     </rPh>
-    <rPh sb="9" eb="11">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="9" eb="11">
       <t>カクニン</t>
     </rPh>
-    <rPh sb="11" eb="12">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="11" eb="12">
       <t>ヒョウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
@@ -238,89 +212,52 @@
       </rPr>
       <t>工程変更理由：（項目BとF、Gは事前申請で承認後生産に移ってください。）</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>コウテイ</t>
     </rPh>
-    <rPh sb="3" eb="5">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="3" eb="5">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="5" eb="7">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="5" eb="7">
       <t>リユウ</t>
     </rPh>
-    <rPh sb="9" eb="11">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="9" eb="11">
       <t>コウモク</t>
     </rPh>
-    <rPh sb="17" eb="19">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="17" eb="19">
       <t>ジゼン</t>
     </rPh>
-    <rPh sb="19" eb="21">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="19" eb="21">
       <t>シンセイ</t>
     </rPh>
-    <rPh sb="22" eb="24">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="22" eb="24">
       <t>ショウニン</t>
     </rPh>
-    <rPh sb="24" eb="25">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="24" eb="25">
       <t>ゴ</t>
     </rPh>
-    <rPh sb="25" eb="27">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="25" eb="27">
       <t>セイサン</t>
     </rPh>
-    <rPh sb="28" eb="29">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="28" eb="29">
       <t>ウツ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> Reason of process change: (Items B, F and G below are required approval prior to start production.)</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> B：加工工場の変更</t>
-    <rPh sb="3" eb="5">
-      <t>カコウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウジョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> Ｆ：材料・副資材の変更</t>
-    <rPh sb="3" eb="5">
-      <t>ザイリョウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シザイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Ｇ：その他（当社の指示項目）</t>
-    <rPh sb="4" eb="5">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウシャ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シジ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="ＭＳ Ｐ明朝"/>
@@ -329,7 +266,7 @@
       </rPr>
       <t>Ｂ</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Times New Roman"/>
@@ -337,10 +274,10 @@
       </rPr>
       <t>: Manufacturing Plant Change</t>
     </r>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="ＭＳ Ｐ明朝"/>
@@ -349,7 +286,7 @@
       </rPr>
       <t>Ｆ</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Times New Roman"/>
@@ -357,17 +294,16 @@
       </rPr>
       <t>: Material Manufacturer /Indirect Material</t>
     </r>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>G: Others (Brother's instructions )</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> 変更予定日</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Times New Roman"/>
@@ -375,16 +311,16 @@
       </rPr>
       <t xml:space="preserve"> (yy/mm/dd)</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>ヘンコウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> Expected date of change</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="ＭＳ Ｐ明朝"/>
@@ -393,13 +329,13 @@
       </rPr>
       <t>　</t>
     </r>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>回答書　</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="12"/>
@@ -408,19 +344,19 @@
       </rPr>
       <t>REPLY SHEET</t>
     </r>
-    <rPh sb="0" eb="2">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="0" eb="2">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="2" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="2" eb="3">
       <t>ショ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> 回答 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
@@ -428,126 +364,70 @@
       </rPr>
       <t>Reply:</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>カイトウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>回答日</t>
-    <rPh sb="0" eb="3">
-      <t>カイトウビ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> &lt;yy.mm.dd&gt;</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>承　認</t>
-    <rPh sb="0" eb="1">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シノブ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>調　査</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>RoHS</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> Relpy Date</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Approved</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve">Checked </t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>回答部門</t>
-    <rPh sb="0" eb="2">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ブモン</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> Reply Section</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <t>Brother Industries, Ltd.  D3-1-1-004JE Rev1.01</t>
-    <phoneticPr fontId="41"/>
+    <t xml:space="preserve">Brother Industries, Ltd.  D3-1-1-004JE Rev1.01</t>
+  </si>
+  <si>
+    <t>J. Asi</t>
   </si>
   <si>
     <t>工 程 変 更 申 請 書</t>
-    <rPh sb="0" eb="1">
-      <t>コウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ホド</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヘン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>サラ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>サル</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ショ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>工 程 变 更 申 请 书</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve">负责人 </t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>公司名称</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>部品名</t>
-    <rPh sb="0" eb="2">
-      <t>ブヒン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>部品代号</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>部品名称</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -556,7 +436,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="MS PGothic"/>
@@ -564,44 +444,44 @@
       </rPr>
       <t>変更内容、変更理由　</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="SimSun"/>
       </rPr>
       <t>変更内容，变更理由:</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="3" eb="5">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="3" eb="5">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="6" eb="8">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="8" eb="10">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="8" eb="10">
       <t>リユウ</t>
     </rPh>
-    <rPh sb="11" eb="13">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="11" eb="13">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="13" eb="15">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="13" eb="15">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="17" eb="18">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="17" eb="18">
       <t>フケル</t>
     </rPh>
-    <rPh sb="18" eb="20">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="18" eb="20">
       <t>リユウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>工程</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
@@ -611,7 +491,7 @@
       </rPr>
       <t>变</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
@@ -623,17 +503,15 @@
   </si>
   <si>
     <t>工程变更理由:(项目B和F、G为事前申请、认可后请投入生产.)</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> B：加工工厂的变更</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> F：材料</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="ＭＳ Ｐ明朝"/>
@@ -642,28 +520,26 @@
       </rPr>
       <t>・</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="9"/>
         <rFont val="SimSun"/>
       </rPr>
       <t>副材料的变更</t>
     </r>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>G：其他(本公司的指示项目)</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> 变更预定日</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>回答書　</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="12"/>
@@ -671,72 +547,59 @@
       </rPr>
       <t>回答书</t>
     </r>
-    <rPh sb="0" eb="2">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="0" eb="2">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="2" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="2" eb="3">
       <t>ショ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> 回答 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="SimSun"/>
       </rPr>
       <t>回答:</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>カイトウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
-  </si>
-  <si>
-    <t>回答日</t>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>批　准</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>调　查</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>回答部门</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Đơn xin thay đổi công đoạn</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Chịu trách nhiệm</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Đảm nhiệm</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Tên công ty</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Mã linh kiện</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Tên linh kiện</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -745,7 +608,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="MS PGothic"/>
@@ -753,7 +616,7 @@
       </rPr>
       <t>変更内容、変更理由</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -762,7 +625,7 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
@@ -770,7 +633,7 @@
       </rPr>
       <t xml:space="preserve">Nội dung thay đổi, lí do thay đổi </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="MS PGothic"/>
@@ -778,79 +641,43 @@
       </rPr>
       <t>：</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="3" eb="5">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="3" eb="5">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="6" eb="8">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="8" eb="10">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="8" eb="10">
       <t>リユウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> 工程変更理由：（項目BとF、Gは事前申請で承認後生産に移ってください。）</t>
-    <rPh sb="1" eb="3">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>リユウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ショウニン</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>セイサン</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ウツ</t>
-    </rPh>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> Lí do thay đổi công đoạn: (hạng mục B,F,G phải gửi yêu cầu trước &amp; chỉ được đi vào sản xuất sau khi nhận được phê duyệt)</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>B:Thay đổi xưởng gia công</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>F: Thay đổi NVL hay NVL phụ</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>G: khác (hạng mục chỉ thị của Brother)</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Expected Date of Change</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>回答書　</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="12"/>
@@ -859,19 +686,19 @@
       </rPr>
       <t>Bản trả lời</t>
     </r>
-    <rPh sb="0" eb="2">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="0" eb="2">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="2" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="2" eb="3">
       <t>ショ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve"> 回答 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
@@ -879,26 +706,22 @@
       </rPr>
       <t>Trả lời:</t>
     </r>
-    <rPh sb="1" eb="3">
+    <rPh xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sb="1" eb="3">
       <t>カイトウ</t>
     </rPh>
-    <phoneticPr fontId="41"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="41"/>
   </si>
   <si>
     <t>Ngày trả lời</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Phê duyệt</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t>Điều tra</t>
-    <phoneticPr fontId="41"/>
   </si>
   <si>
     <t xml:space="preserve"> Bộ phận trả lời</t>
-    <phoneticPr fontId="41"/>
   </si>
 </sst>
 </file>
@@ -908,14 +731,14 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;\-#,##0.00"/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="61">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1174,13 +997,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1190,8 +1006,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1212,8 +1028,8 @@
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="3"/>
+      <scheme val="minor"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1243,8 +1059,8 @@
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="3"/>
+      <scheme val="minor"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1257,8 +1073,8 @@
       <sz val="12"/>
       <name val="Cambria"/>
       <family val="3"/>
+      <scheme val="major"/>
       <charset val="128"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1269,15 +1085,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="3"/>
+      <scheme val="minor"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1292,16 +1101,10 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1310,10 +1113,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="SimSun"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="SimSun"/>
     </font>
   </fonts>
@@ -2122,1095 +1921,1359 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="5" fillId="0" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="246">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="93" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="340">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="5" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="5" applyFill="1" borderId="0" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="5" applyFill="1" borderId="0" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="24" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="5" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="25" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="49" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="50" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="26" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="51" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="27" applyFont="1" fillId="20" applyFill="1" borderId="4" applyBorder="1" xfId="52" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="53" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="22" applyFill="1" borderId="5" applyBorder="1" xfId="54" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="29" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="55" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="56" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="39" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" xfId="57" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="37" applyFont="1" fillId="23" applyFill="1" borderId="12" applyBorder="1" xfId="58" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="59" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="60" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="61" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="62" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="63" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="64" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="65" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="66" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="67" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="30" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="68" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="69" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="70" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="0" applyFill="1" borderId="9" applyBorder="1" xfId="71" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="10" applyBorder="1" xfId="72" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="73" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="20" applyFill="1" borderId="4" applyBorder="1" xfId="74" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="75" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="76" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="22" applyFill="1" borderId="5" applyBorder="1" xfId="77" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="40" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="78" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="33" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="79" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="34" applyFont="1" fillId="0" applyFill="1" borderId="9" applyBorder="1" xfId="80" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="35" applyFont="1" fillId="0" applyFill="1" borderId="10" applyBorder="1" xfId="81" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="35" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="82" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="83" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="31" applyFont="1" fillId="23" applyFill="1" borderId="7" applyBorder="1" xfId="84" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="38" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="85" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="32" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="86" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="87" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="23" applyFill="1" borderId="7" applyBorder="1" xfId="88" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" xfId="89" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="12" applyBorder="1" xfId="90" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="22" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="91" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="92" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="23" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="93" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="36" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="94" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="41" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="50" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="43" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="47" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="43" applyFont="1" fillId="24" applyFill="1" borderId="49" applyBorder="1" xfId="0" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="43" applyFont="1" fillId="24" applyFill="1" borderId="55" applyBorder="1" xfId="0" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="54" applyFont="1" fillId="0" applyFill="1" borderId="36" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="27" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="25" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="25" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="25" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="57" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="24" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="0" applyFill="1" borderId="31" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="48" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="51" applyFont="1" fillId="24" applyFill="1" borderId="36" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="24" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="51" applyFont="1" fillId="24" applyFill="1" borderId="31" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="24" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="51" applyFont="1" fillId="24" applyFill="1" borderId="39" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="40" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="39" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="31" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="44" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="52" applyFont="1" fillId="24" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="52" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="52" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="24" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="24" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="57" applyFont="1" fillId="25" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="50" applyFont="1" fillId="24" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="50" applyFont="1" fillId="24" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="24" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="50" applyFont="1" fillId="24" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="45" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="46" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="47" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="30" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="25" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="47" applyFont="1" fillId="24" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="58" applyFont="1" fillId="24" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="58" applyFont="1" fillId="24" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="24" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="49" applyFont="1" fillId="24" applyFill="1" borderId="30" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="49" applyFont="1" fillId="24" applyFill="1" borderId="25" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="49" applyFont="1" fillId="24" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="58" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="58" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="54" applyFont="1" fillId="0" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="24" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="53" applyFont="1" fillId="24" applyFill="1" borderId="41" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="24" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="53" applyFont="1" fillId="24" applyFill="1" borderId="42" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="24" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="53" applyFont="1" fillId="24" applyFill="1" borderId="43" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="51" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="37" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="42" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="17" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="19" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="27" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="48" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="49" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="55" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="25" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="54" applyFont="1" fillId="25" applyFill="1" borderId="48" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="25" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="54" applyFont="1" fillId="25" applyFill="1" borderId="49" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="25" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="54" applyFont="1" fillId="25" applyFill="1" borderId="50" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="37" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="46" applyFont="1" fillId="0" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="46" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="46" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="46" applyFont="1" fillId="0" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="46" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="46" applyFont="1" fillId="0" applyFill="1" borderId="37" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="43" applyFont="1" fillId="24" applyFill="1" borderId="56" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="43" applyFont="1" fillId="24" applyFill="1" borderId="57" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="38" applyBorder="1" xfId="0" quotePrefix="1" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" quotePrefix="1" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="43" applyFont="1" fillId="24" applyFill="1" borderId="58" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="14" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="46" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="59" applyFont="1" fillId="24" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="59" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="59" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="26" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="53" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="35" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="55" applyFont="1" fillId="25" applyFill="1" borderId="54" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="37" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="55" applyFont="1" fillId="0" applyFill="1" borderId="37" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="34" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="51" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="52" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="48" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="49" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="25" applyFill="1" borderId="50" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="45" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="46" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="47" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="30" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="25" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="27" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="24" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="60" applyFont="1" fillId="24" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="56" applyFont="1" fillId="24" applyFill="1" borderId="21" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="56" applyFont="1" fillId="24" applyFill="1" borderId="23" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="22" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="24" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="38" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="45" applyFont="1" fillId="24" applyFill="1" borderId="20" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="29" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="48" applyFont="1" fillId="24" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="18" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="13" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="32" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="44" applyFont="1" fillId="0" applyFill="1" borderId="37" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="95">
-    <cellStyle name="_01 成形監査Check Sheet2012" xfId="93" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="_LS2198001PRINTED EX PANEL 寸法不良报告" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - アクセント 1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - アクセント 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - アクセント 3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - アクセント 4 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - アクセント 5 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - アクセント 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="13" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="14" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="15" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="40% - アクセント 1 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="40% - アクセント 2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="40% - アクセント 3 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="40% - アクセント 4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="40% - アクセント 5 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="40% - アクセント 6 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="22" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="24" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="25" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="26" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="27" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="60% - アクセント 1 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="60% - アクセント 2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="60% - アクセント 3 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="60% - アクセント 4 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="60% - アクセント 5 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="60% - アクセント 6 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="34" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="37" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="38" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="39" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="DELTA" xfId="40" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="Header1" xfId="41" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="Header2" xfId="42" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="_01 成形監査Check Sheet2012" xfId="1"/>
+    <cellStyle name="_LS2198001PRINTED EX PANEL 寸法不良报告" xfId="2"/>
+    <cellStyle name="20% - アクセント 1 2" xfId="3"/>
+    <cellStyle name="20% - アクセント 2 2" xfId="4"/>
+    <cellStyle name="20% - アクセント 3 2" xfId="5"/>
+    <cellStyle name="20% - アクセント 4 2" xfId="6"/>
+    <cellStyle name="20% - アクセント 5 2" xfId="7"/>
+    <cellStyle name="20% - アクセント 6 2" xfId="8"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="9"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="10"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="11"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="12"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="13"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="14"/>
+    <cellStyle name="40% - アクセント 1 2" xfId="15"/>
+    <cellStyle name="40% - アクセント 2 2" xfId="16"/>
+    <cellStyle name="40% - アクセント 3 2" xfId="17"/>
+    <cellStyle name="40% - アクセント 4 2" xfId="18"/>
+    <cellStyle name="40% - アクセント 5 2" xfId="19"/>
+    <cellStyle name="40% - アクセント 6 2" xfId="20"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="21"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="22"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="23"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="24"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="25"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="26"/>
+    <cellStyle name="60% - アクセント 1 2" xfId="27"/>
+    <cellStyle name="60% - アクセント 2 2" xfId="28"/>
+    <cellStyle name="60% - アクセント 3 2" xfId="29"/>
+    <cellStyle name="60% - アクセント 4 2" xfId="30"/>
+    <cellStyle name="60% - アクセント 5 2" xfId="31"/>
+    <cellStyle name="60% - アクセント 6 2" xfId="32"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="33"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="34"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="37"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="38"/>
+    <cellStyle name="DELTA" xfId="39"/>
+    <cellStyle name="Header1" xfId="40"/>
+    <cellStyle name="Header2" xfId="41"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="94" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="Normal 3" xfId="92" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="アクセント 1 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="アクセント 2 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="アクセント 3 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="アクセント 4 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="アクセント 5 2" xfId="47" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="アクセント 6 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="スタイル 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="タイトル 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="チェック セル 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="どちらでもない 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="メモ 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="リンク セル 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="一般_LF4991-0 09-Mar-04" xfId="55" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="入力 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="出力 2" xfId="67" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="好" xfId="64" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="差" xfId="65" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="常规_TEST RUN依赖书(REC9999020C)" xfId="68" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="强调文字颜色 1" xfId="74" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="强调文字颜色 2" xfId="75" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="强调文字颜色 3" xfId="76" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="强调文字颜色 4" xfId="77" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="强调文字颜色 5" xfId="78" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="强调文字颜色 6" xfId="79" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="悪い 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="标题" xfId="80" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="标题 1" xfId="81" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="标题 2" xfId="82" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="标题 3" xfId="83" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="标题 4" xfId="84" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="检查单元格" xfId="85" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="汇总" xfId="86" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="注释" xfId="70" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="良い 2" xfId="73" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="見出し 1 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="見出し 2 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="見出し 3 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="見出し 4 2" xfId="63" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="解释性文本" xfId="56" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="計算 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="説明文 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="警告文 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="警告文本" xfId="59" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="计算" xfId="87" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="输入" xfId="89" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="输出" xfId="88" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="适中" xfId="90" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="通貨 [0.00] 2" xfId="71" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="链接单元格" xfId="91" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="集計 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Normal 2" xfId="42"/>
+    <cellStyle name="Normal 3" xfId="43"/>
+    <cellStyle name="アクセント 1 2" xfId="44"/>
+    <cellStyle name="アクセント 2 2" xfId="45"/>
+    <cellStyle name="アクセント 3 2" xfId="46"/>
+    <cellStyle name="アクセント 4 2" xfId="47"/>
+    <cellStyle name="アクセント 5 2" xfId="48"/>
+    <cellStyle name="アクセント 6 2" xfId="49"/>
+    <cellStyle name="スタイル 1" xfId="50"/>
+    <cellStyle name="タイトル 2" xfId="51"/>
+    <cellStyle name="チェック セル 2" xfId="52"/>
+    <cellStyle name="どちらでもない 2" xfId="53"/>
+    <cellStyle name="メモ 2" xfId="54"/>
+    <cellStyle name="リンク セル 2" xfId="55"/>
+    <cellStyle name="一般_LF4991-0 09-Mar-04" xfId="56"/>
+    <cellStyle name="入力 2" xfId="57"/>
+    <cellStyle name="出力 2" xfId="58"/>
+    <cellStyle name="好" xfId="59"/>
+    <cellStyle name="差" xfId="60"/>
+    <cellStyle name="常规_TEST RUN依赖书(REC9999020C)" xfId="61"/>
+    <cellStyle name="强调文字颜色 1" xfId="62"/>
+    <cellStyle name="强调文字颜色 2" xfId="63"/>
+    <cellStyle name="强调文字颜色 3" xfId="64"/>
+    <cellStyle name="强调文字颜色 4" xfId="65"/>
+    <cellStyle name="强调文字颜色 5" xfId="66"/>
+    <cellStyle name="强调文字颜色 6" xfId="67"/>
+    <cellStyle name="悪い 2" xfId="68"/>
+    <cellStyle name="标题" xfId="69"/>
+    <cellStyle name="标题 1" xfId="70"/>
+    <cellStyle name="标题 2" xfId="71"/>
+    <cellStyle name="标题 3" xfId="72"/>
+    <cellStyle name="标题 4" xfId="73"/>
+    <cellStyle name="检查单元格" xfId="74"/>
+    <cellStyle name="標準 2" xfId="75"/>
+    <cellStyle name="汇总" xfId="76"/>
+    <cellStyle name="注释" xfId="77"/>
+    <cellStyle name="良い 2" xfId="78"/>
+    <cellStyle name="見出し 1 2" xfId="79"/>
+    <cellStyle name="見出し 2 2" xfId="80"/>
+    <cellStyle name="見出し 3 2" xfId="81"/>
+    <cellStyle name="見出し 4 2" xfId="82"/>
+    <cellStyle name="解释性文本" xfId="83"/>
+    <cellStyle name="計算 2" xfId="84"/>
+    <cellStyle name="説明文 2" xfId="85"/>
+    <cellStyle name="警告文 2" xfId="86"/>
+    <cellStyle name="警告文本" xfId="87"/>
+    <cellStyle name="计算" xfId="88"/>
+    <cellStyle name="输入" xfId="89"/>
+    <cellStyle name="输出" xfId="90"/>
+    <cellStyle name="适中" xfId="91"/>
+    <cellStyle name="通貨 [0.00] 2" xfId="92"/>
+    <cellStyle name="链接单元格" xfId="93"/>
+    <cellStyle name="集計 2" xfId="94"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4149,7 +4212,8 @@
                 <a:latin typeface="Century" panose="02040604050505020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> </a:t>
+              <a:t>
+              </a:t>
             </a:r>
             <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" u="sng">
               <a:solidFill>
@@ -5720,7 +5784,8 @@
                 <a:latin typeface="Century" panose="02040604050505020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> </a:t>
+              <a:t>
+              </a:t>
             </a:r>
             <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" u="sng">
               <a:solidFill>
@@ -7015,7 +7080,8 @@
                 <a:latin typeface="Century" panose="02040604050505020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> </a:t>
+              <a:t>
+              </a:t>
             </a:r>
             <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" u="sng">
               <a:solidFill>
@@ -7507,1070 +7573,1102 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:T49"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="0.85546875" style="2" customWidth="1"/>
-    <col min="2" max="20" width="4.28515625" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1" style="96"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1" style="96"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1" style="96"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1" style="96"/>
+    <col min="5" max="5" width="4.28515625" customWidth="1" style="96"/>
+    <col min="6" max="6" width="4.28515625" customWidth="1" style="96"/>
+    <col min="7" max="7" width="4.28515625" customWidth="1" style="96"/>
+    <col min="8" max="8" width="4.28515625" customWidth="1" style="96"/>
+    <col min="9" max="9" width="4.28515625" customWidth="1" style="96"/>
+    <col min="10" max="10" width="4.28515625" customWidth="1" style="96"/>
+    <col min="11" max="11" width="4.28515625" customWidth="1" style="96"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1" style="96"/>
+    <col min="13" max="13" width="4.28515625" customWidth="1" style="96"/>
+    <col min="14" max="14" width="4.28515625" customWidth="1" style="96"/>
+    <col min="15" max="15" width="4.28515625" customWidth="1" style="96"/>
+    <col min="16" max="16" width="4.28515625" customWidth="1" style="96"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1" style="96"/>
+    <col min="18" max="18" width="4.28515625" customWidth="1" style="96"/>
+    <col min="19" max="19" width="4.28515625" customWidth="1" style="96"/>
+    <col min="20" max="20" width="4.28515625" customWidth="1" style="96"/>
+    <col min="21" max="16384" width="9" customWidth="1" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20">
-      <c r="B1" s="1"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="2:20">
-      <c r="B2" s="4"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:20" ht="15.75" thickBot="1">
-      <c r="C3" s="5" t="s">
+    <row r="1">
+      <c r="B1" s="95"/>
+      <c r="G1" s="97"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="98"/>
+      <c r="G2" s="99"/>
+    </row>
+    <row r="3" ht="15.75">
+      <c r="C3" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="P3" s="22" t="s">
+      <c r="N3" s="97"/>
+      <c r="P3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="144"/>
-      <c r="R3" s="144"/>
-      <c r="S3" s="144"/>
-      <c r="T3" s="144"/>
-    </row>
-    <row r="4" spans="2:20" ht="18.75" customHeight="1">
-      <c r="B4" s="53" t="s">
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="238"/>
+      <c r="T3" s="238"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="B4" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="56" t="s">
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="148"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="148"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="57"/>
-      <c r="S4" s="58" t="s">
+      <c r="R4" s="151"/>
+      <c r="S4" s="152" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="59"/>
-    </row>
-    <row r="5" spans="2:20" ht="16.5" customHeight="1">
-      <c r="B5" s="60" t="s">
+      <c r="T4" s="153"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="B5" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="63" t="s">
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="156"/>
+      <c r="Q5" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="64"/>
-      <c r="S5" s="65" t="s">
+      <c r="R5" s="158"/>
+      <c r="S5" s="159" t="s">
         <v>7</v>
       </c>
-      <c r="T5" s="66"/>
-    </row>
-    <row r="6" spans="2:20" ht="12" customHeight="1">
-      <c r="B6" s="67"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="77"/>
-    </row>
-    <row r="7" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B7" s="80" t="s">
+      <c r="T5" s="160"/>
+    </row>
+    <row r="6" ht="12" customHeight="1">
+      <c r="B6" s="161"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
+      <c r="Q6" s="164"/>
+      <c r="R6" s="165"/>
+      <c r="S6" s="170"/>
+      <c r="T6" s="171"/>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="B7" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="85" t="s">
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="177"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="177"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="87"/>
-      <c r="P7" s="88"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="72"/>
-      <c r="T7" s="78"/>
-    </row>
-    <row r="8" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B8" s="92" t="s">
+      <c r="L7" s="176"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="181"/>
+      <c r="O7" s="181"/>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="166"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="166"/>
+      <c r="T7" s="172"/>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="B8" s="186" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="63" t="s">
+      <c r="C8" s="159"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="168"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="64"/>
-      <c r="M8" s="89"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="79"/>
-    </row>
-    <row r="9" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B9" s="80" t="s">
+      <c r="L8" s="158"/>
+      <c r="M8" s="183"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="169"/>
+      <c r="S8" s="168"/>
+      <c r="T8" s="173"/>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="B9" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="85" t="s">
+      <c r="C9" s="175"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="177"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="179" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="82"/>
-      <c r="M9" s="160"/>
-      <c r="N9" s="161"/>
-      <c r="O9" s="161"/>
-      <c r="P9" s="161"/>
-      <c r="Q9" s="161"/>
-      <c r="R9" s="161"/>
-      <c r="S9" s="161"/>
-      <c r="T9" s="162"/>
-    </row>
-    <row r="10" spans="2:20" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B10" s="93" t="s">
+      <c r="L9" s="176"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="255"/>
+      <c r="O9" s="255"/>
+      <c r="P9" s="255"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="256"/>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="B10" s="187" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="181"/>
-      <c r="M10" s="163"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
-      <c r="P10" s="164"/>
-      <c r="Q10" s="164"/>
-      <c r="R10" s="164"/>
-      <c r="S10" s="164"/>
-      <c r="T10" s="165"/>
-    </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1">
-      <c r="B11" s="16" t="s">
+      <c r="C10" s="188"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="274"/>
+      <c r="L10" s="275"/>
+      <c r="M10" s="257"/>
+      <c r="N10" s="258"/>
+      <c r="O10" s="258"/>
+      <c r="P10" s="258"/>
+      <c r="Q10" s="258"/>
+      <c r="R10" s="258"/>
+      <c r="S10" s="258"/>
+      <c r="T10" s="259"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="151" t="s">
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="245" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="152"/>
-      <c r="O11" s="152"/>
-      <c r="P11" s="152"/>
-      <c r="Q11" s="153"/>
-      <c r="R11" s="154"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="156"/>
-    </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1">
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="25"/>
-    </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1">
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="25"/>
-    </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1">
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="25"/>
-    </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1">
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="25"/>
-    </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1">
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="25"/>
-    </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1">
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="25"/>
-    </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1">
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="25"/>
-    </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="25"/>
-    </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1">
-      <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="25"/>
-    </row>
-    <row r="21" spans="2:20" ht="18" customHeight="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="25"/>
-    </row>
-    <row r="22" spans="2:20" ht="18" customHeight="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="25"/>
-    </row>
-    <row r="23" spans="2:20" ht="18" customHeight="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="25"/>
-    </row>
-    <row r="24" spans="2:20" ht="18" customHeight="1">
-      <c r="B24" s="23"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="25"/>
-    </row>
-    <row r="25" spans="2:20" ht="18" customHeight="1">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="28"/>
-    </row>
-    <row r="26" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B26" s="96" t="s">
+      <c r="N11" s="246"/>
+      <c r="O11" s="246"/>
+      <c r="P11" s="246"/>
+      <c r="Q11" s="247"/>
+      <c r="R11" s="248"/>
+      <c r="S11" s="249"/>
+      <c r="T11" s="250"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="119"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="117"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
+      <c r="T13" s="119"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="117"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="118"/>
+      <c r="T14" s="119"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="117"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="118"/>
+      <c r="T15" s="119"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="117"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="118"/>
+      <c r="T16" s="119"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="117"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="118"/>
+      <c r="P17" s="118"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="119"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="117"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="118"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="118"/>
+      <c r="T18" s="119"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="118"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="118"/>
+      <c r="T19" s="119"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="118"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="118"/>
+      <c r="T20" s="119"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="117"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="118"/>
+      <c r="S21" s="118"/>
+      <c r="T21" s="119"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="117"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="118"/>
+      <c r="Q22" s="118"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="118"/>
+      <c r="T22" s="119"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="118"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="118"/>
+      <c r="S23" s="118"/>
+      <c r="T23" s="119"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="117"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="118"/>
+      <c r="Q24" s="118"/>
+      <c r="R24" s="118"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="119"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="121"/>
+      <c r="R25" s="121"/>
+      <c r="S25" s="121"/>
+      <c r="T25" s="122"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="B26" s="190" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
-      <c r="L26" s="97"/>
-      <c r="M26" s="97"/>
-      <c r="N26" s="97"/>
-      <c r="O26" s="97"/>
-      <c r="P26" s="97"/>
-      <c r="Q26" s="97"/>
-      <c r="R26" s="97"/>
-      <c r="S26" s="97"/>
-      <c r="T26" s="98"/>
-    </row>
-    <row r="27" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B27" s="99" t="s">
+      <c r="C26" s="191"/>
+      <c r="D26" s="191"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="191"/>
+      <c r="I26" s="191"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="191"/>
+      <c r="N26" s="191"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="191"/>
+      <c r="Q26" s="191"/>
+      <c r="R26" s="191"/>
+      <c r="S26" s="191"/>
+      <c r="T26" s="192"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="B27" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="100"/>
-      <c r="N27" s="100"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="100"/>
-      <c r="Q27" s="100"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="100"/>
-      <c r="T27" s="101"/>
-    </row>
-    <row r="28" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B28" s="172" t="s">
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="194"/>
+      <c r="L27" s="194"/>
+      <c r="M27" s="194"/>
+      <c r="N27" s="194"/>
+      <c r="O27" s="194"/>
+      <c r="P27" s="194"/>
+      <c r="Q27" s="194"/>
+      <c r="R27" s="194"/>
+      <c r="S27" s="194"/>
+      <c r="T27" s="195"/>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="B28" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="173"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="173" t="s">
+      <c r="C28" s="267"/>
+      <c r="D28" s="267"/>
+      <c r="E28" s="267"/>
+      <c r="F28" s="267"/>
+      <c r="G28" s="267"/>
+      <c r="H28" s="267" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="173"/>
-      <c r="J28" s="173"/>
-      <c r="K28" s="173"/>
-      <c r="L28" s="173"/>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="173" t="s">
+      <c r="I28" s="267"/>
+      <c r="J28" s="267"/>
+      <c r="K28" s="267"/>
+      <c r="L28" s="267"/>
+      <c r="M28" s="267"/>
+      <c r="N28" s="267"/>
+      <c r="O28" s="267" t="s">
         <v>21</v>
       </c>
-      <c r="P28" s="173"/>
-      <c r="Q28" s="173"/>
-      <c r="R28" s="173"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="178"/>
-    </row>
-    <row r="29" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B29" s="174" t="s">
+      <c r="P28" s="267"/>
+      <c r="Q28" s="267"/>
+      <c r="R28" s="267"/>
+      <c r="S28" s="267"/>
+      <c r="T28" s="272"/>
+    </row>
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="B29" s="268" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="175"/>
-      <c r="D29" s="175"/>
-      <c r="E29" s="175"/>
-      <c r="F29" s="175"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="176" t="s">
+      <c r="C29" s="269"/>
+      <c r="D29" s="269"/>
+      <c r="E29" s="269"/>
+      <c r="F29" s="269"/>
+      <c r="G29" s="269"/>
+      <c r="H29" s="270" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="177"/>
-      <c r="J29" s="177"/>
-      <c r="K29" s="177"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="177"/>
-      <c r="N29" s="177"/>
-      <c r="O29" s="177" t="s">
+      <c r="I29" s="271"/>
+      <c r="J29" s="271"/>
+      <c r="K29" s="271"/>
+      <c r="L29" s="271"/>
+      <c r="M29" s="271"/>
+      <c r="N29" s="271"/>
+      <c r="O29" s="271" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="177"/>
-      <c r="Q29" s="177"/>
-      <c r="R29" s="177"/>
-      <c r="S29" s="177"/>
-      <c r="T29" s="179"/>
-    </row>
-    <row r="30" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B30" s="145" t="s">
+      <c r="P29" s="271"/>
+      <c r="Q29" s="271"/>
+      <c r="R29" s="271"/>
+      <c r="S29" s="271"/>
+      <c r="T29" s="273"/>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="B30" s="239" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="146"/>
-      <c r="D30" s="146"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="147"/>
-      <c r="H30" s="166"/>
-      <c r="I30" s="167"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="167"/>
-      <c r="L30" s="167"/>
-      <c r="M30" s="167"/>
-      <c r="N30" s="167"/>
-      <c r="O30" s="167"/>
-      <c r="P30" s="167"/>
-      <c r="Q30" s="167"/>
-      <c r="R30" s="167"/>
-      <c r="S30" s="167"/>
-      <c r="T30" s="168"/>
-    </row>
-    <row r="31" spans="2:20" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B31" s="148" t="s">
+      <c r="C30" s="240"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="241"/>
+      <c r="H30" s="260"/>
+      <c r="I30" s="261"/>
+      <c r="J30" s="261"/>
+      <c r="K30" s="261"/>
+      <c r="L30" s="261"/>
+      <c r="M30" s="261"/>
+      <c r="N30" s="261"/>
+      <c r="O30" s="261"/>
+      <c r="P30" s="261"/>
+      <c r="Q30" s="261"/>
+      <c r="R30" s="261"/>
+      <c r="S30" s="261"/>
+      <c r="T30" s="262"/>
+    </row>
+    <row r="31" ht="13.5" customHeight="1">
+      <c r="B31" s="242" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="149"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="150"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
-      <c r="P31" s="170"/>
-      <c r="Q31" s="170"/>
-      <c r="R31" s="170"/>
-      <c r="S31" s="170"/>
-      <c r="T31" s="171"/>
-    </row>
-    <row r="32" spans="2:20" ht="6" customHeight="1" thickBot="1">
-      <c r="B32" s="6"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
-    </row>
-    <row r="33" spans="2:20" ht="18" customHeight="1">
-      <c r="B33" s="124" t="s">
+      <c r="C31" s="243"/>
+      <c r="D31" s="243"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="263"/>
+      <c r="I31" s="264"/>
+      <c r="J31" s="264"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
+      <c r="M31" s="264"/>
+      <c r="N31" s="264"/>
+      <c r="O31" s="264"/>
+      <c r="P31" s="264"/>
+      <c r="Q31" s="264"/>
+      <c r="R31" s="264"/>
+      <c r="S31" s="264"/>
+      <c r="T31" s="265"/>
+    </row>
+    <row r="32" ht="6" customHeight="1">
+      <c r="B32" s="100"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="107"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="107"/>
+      <c r="R32" s="107"/>
+      <c r="S32" s="107"/>
+      <c r="T32" s="107"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="218" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="125"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="125"/>
-      <c r="R33" s="125"/>
-      <c r="S33" s="125"/>
-      <c r="T33" s="126"/>
-    </row>
-    <row r="34" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B34" s="115" t="s">
+      <c r="C33" s="219"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="219"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="219"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="219"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="219"/>
+      <c r="Q33" s="219"/>
+      <c r="R33" s="219"/>
+      <c r="S33" s="219"/>
+      <c r="T33" s="220"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B34" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="116"/>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="21"/>
-    </row>
-    <row r="35" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="30"/>
-    </row>
-    <row r="36" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="30"/>
-    </row>
-    <row r="37" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="30"/>
-    </row>
-    <row r="38" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="30"/>
-    </row>
-    <row r="39" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B39" s="31"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="30"/>
-    </row>
-    <row r="40" spans="2:20" ht="18" customHeight="1">
-      <c r="B40" s="31"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="30"/>
-    </row>
-    <row r="41" spans="2:20" ht="18" customHeight="1">
-      <c r="B41" s="31"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="30"/>
-    </row>
-    <row r="42" spans="2:20" ht="18" customHeight="1">
-      <c r="B42" s="31"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="30"/>
-    </row>
-    <row r="43" spans="2:20" ht="18" customHeight="1">
-      <c r="B43" s="32"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="33"/>
-      <c r="T43" s="34"/>
-    </row>
-    <row r="44" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B44" s="104" t="s">
+      <c r="C34" s="210"/>
+      <c r="D34" s="210"/>
+      <c r="E34" s="210"/>
+      <c r="F34" s="210"/>
+      <c r="G34" s="210"/>
+      <c r="H34" s="210"/>
+      <c r="I34" s="210"/>
+      <c r="J34" s="210"/>
+      <c r="K34" s="210"/>
+      <c r="L34" s="114"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="114"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="114"/>
+      <c r="Q34" s="114"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="114"/>
+      <c r="T34" s="115"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B35" s="117"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="123"/>
+      <c r="M35" s="123"/>
+      <c r="N35" s="123"/>
+      <c r="O35" s="123"/>
+      <c r="P35" s="123"/>
+      <c r="Q35" s="123"/>
+      <c r="R35" s="123"/>
+      <c r="S35" s="123"/>
+      <c r="T35" s="124"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="118"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="123"/>
+      <c r="M36" s="123"/>
+      <c r="N36" s="123"/>
+      <c r="O36" s="123"/>
+      <c r="P36" s="123"/>
+      <c r="Q36" s="123"/>
+      <c r="R36" s="123"/>
+      <c r="S36" s="123"/>
+      <c r="T36" s="124"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B37" s="117"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="123"/>
+      <c r="M37" s="123"/>
+      <c r="N37" s="123"/>
+      <c r="O37" s="123"/>
+      <c r="P37" s="123"/>
+      <c r="Q37" s="123"/>
+      <c r="R37" s="123"/>
+      <c r="S37" s="123"/>
+      <c r="T37" s="124"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B38" s="117"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="123"/>
+      <c r="M38" s="123"/>
+      <c r="N38" s="123"/>
+      <c r="O38" s="123"/>
+      <c r="P38" s="123"/>
+      <c r="Q38" s="123"/>
+      <c r="R38" s="123"/>
+      <c r="S38" s="123"/>
+      <c r="T38" s="124"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B39" s="125"/>
+      <c r="C39" s="123"/>
+      <c r="D39" s="123"/>
+      <c r="E39" s="123"/>
+      <c r="F39" s="123"/>
+      <c r="G39" s="123"/>
+      <c r="H39" s="123"/>
+      <c r="I39" s="123"/>
+      <c r="J39" s="123"/>
+      <c r="K39" s="123"/>
+      <c r="L39" s="123"/>
+      <c r="M39" s="123"/>
+      <c r="N39" s="123"/>
+      <c r="O39" s="123"/>
+      <c r="P39" s="123"/>
+      <c r="Q39" s="123"/>
+      <c r="R39" s="123"/>
+      <c r="S39" s="123"/>
+      <c r="T39" s="124"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="125"/>
+      <c r="C40" s="123"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="123"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="123"/>
+      <c r="I40" s="123"/>
+      <c r="J40" s="123"/>
+      <c r="K40" s="123"/>
+      <c r="L40" s="123"/>
+      <c r="M40" s="123"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="123"/>
+      <c r="P40" s="123"/>
+      <c r="Q40" s="123"/>
+      <c r="R40" s="123"/>
+      <c r="S40" s="123"/>
+      <c r="T40" s="124"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="125"/>
+      <c r="C41" s="123"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="123"/>
+      <c r="J41" s="123"/>
+      <c r="K41" s="123"/>
+      <c r="L41" s="123"/>
+      <c r="M41" s="123"/>
+      <c r="N41" s="123"/>
+      <c r="O41" s="123"/>
+      <c r="P41" s="123"/>
+      <c r="Q41" s="123"/>
+      <c r="R41" s="123"/>
+      <c r="S41" s="123"/>
+      <c r="T41" s="124"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="125"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="123"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="123"/>
+      <c r="H42" s="123"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="123"/>
+      <c r="R42" s="123"/>
+      <c r="S42" s="123"/>
+      <c r="T42" s="124"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="126"/>
+      <c r="C43" s="127"/>
+      <c r="D43" s="127"/>
+      <c r="E43" s="127"/>
+      <c r="F43" s="127"/>
+      <c r="G43" s="127"/>
+      <c r="H43" s="127"/>
+      <c r="I43" s="127"/>
+      <c r="J43" s="127"/>
+      <c r="K43" s="127"/>
+      <c r="L43" s="127"/>
+      <c r="M43" s="127"/>
+      <c r="N43" s="127"/>
+      <c r="O43" s="127"/>
+      <c r="P43" s="127"/>
+      <c r="Q43" s="127"/>
+      <c r="R43" s="127"/>
+      <c r="S43" s="127"/>
+      <c r="T43" s="128"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1">
+      <c r="B44" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="105"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="12" t="s">
+      <c r="C44" s="199"/>
+      <c r="D44" s="200"/>
+      <c r="E44" s="106" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="107"/>
-      <c r="J44" s="107"/>
-      <c r="K44" s="108" t="s">
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="201"/>
+      <c r="J44" s="201"/>
+      <c r="K44" s="202" t="s">
         <v>31</v>
       </c>
-      <c r="L44" s="109"/>
-      <c r="M44" s="110" t="s">
+      <c r="L44" s="203"/>
+      <c r="M44" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="N44" s="103"/>
-      <c r="O44" s="110" t="s">
+      <c r="N44" s="197"/>
+      <c r="O44" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="P44" s="103"/>
-      <c r="Q44" s="110" t="s">
+      <c r="P44" s="197"/>
+      <c r="Q44" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="103"/>
-      <c r="S44" s="111" t="s">
+      <c r="R44" s="197"/>
+      <c r="S44" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="T44" s="112"/>
-    </row>
-    <row r="45" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B45" s="120" t="s">
+      <c r="T44" s="206"/>
+    </row>
+    <row r="45" ht="13.5" customHeight="1">
+      <c r="B45" s="214" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="121"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
-      <c r="H45" s="119"/>
-      <c r="I45" s="123"/>
-      <c r="J45" s="123"/>
-      <c r="K45" s="102" t="s">
+      <c r="C45" s="215"/>
+      <c r="D45" s="216"/>
+      <c r="E45" s="211"/>
+      <c r="F45" s="212"/>
+      <c r="G45" s="212"/>
+      <c r="H45" s="213"/>
+      <c r="I45" s="217"/>
+      <c r="J45" s="217"/>
+      <c r="K45" s="196" t="s">
         <v>35</v>
       </c>
-      <c r="L45" s="103"/>
-      <c r="M45" s="102" t="s">
+      <c r="L45" s="197"/>
+      <c r="M45" s="196" t="s">
         <v>36</v>
       </c>
-      <c r="N45" s="103"/>
-      <c r="O45" s="102" t="s">
+      <c r="N45" s="197"/>
+      <c r="O45" s="196" t="s">
         <v>36</v>
       </c>
-      <c r="P45" s="103"/>
-      <c r="Q45" s="102" t="s">
+      <c r="P45" s="197"/>
+      <c r="Q45" s="196" t="s">
         <v>7</v>
       </c>
-      <c r="R45" s="103"/>
-      <c r="S45" s="113"/>
-      <c r="T45" s="114"/>
-    </row>
-    <row r="46" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B46" s="104" t="s">
+      <c r="R45" s="197"/>
+      <c r="S45" s="207"/>
+      <c r="T45" s="208"/>
+    </row>
+    <row r="46" ht="13.5" customHeight="1">
+      <c r="B46" s="198" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="105"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="135"/>
-      <c r="F46" s="136"/>
-      <c r="G46" s="136"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="135"/>
-      <c r="J46" s="137"/>
-      <c r="K46" s="135"/>
-      <c r="L46" s="137"/>
-      <c r="M46" s="127"/>
-      <c r="N46" s="127"/>
-      <c r="O46" s="127"/>
-      <c r="P46" s="127"/>
-      <c r="Q46" s="127"/>
-      <c r="R46" s="127"/>
-      <c r="S46" s="129"/>
-      <c r="T46" s="130"/>
-    </row>
-    <row r="47" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B47" s="120" t="s">
+      <c r="C46" s="199"/>
+      <c r="D46" s="200"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="230"/>
+      <c r="G46" s="230"/>
+      <c r="H46" s="231"/>
+      <c r="I46" s="229"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="229"/>
+      <c r="L46" s="231"/>
+      <c r="M46" s="221"/>
+      <c r="N46" s="221"/>
+      <c r="O46" s="221"/>
+      <c r="P46" s="221"/>
+      <c r="Q46" s="221"/>
+      <c r="R46" s="221"/>
+      <c r="S46" s="223"/>
+      <c r="T46" s="224"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="B47" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="121"/>
-      <c r="D47" s="122"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="140"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="140"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="140"/>
-      <c r="M47" s="127"/>
-      <c r="N47" s="127"/>
-      <c r="O47" s="127"/>
-      <c r="P47" s="127"/>
-      <c r="Q47" s="127"/>
-      <c r="R47" s="127"/>
-      <c r="S47" s="131"/>
-      <c r="T47" s="132"/>
-    </row>
-    <row r="48" spans="2:20" ht="12" customHeight="1" thickBot="1">
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="141"/>
-      <c r="J48" s="143"/>
-      <c r="K48" s="141"/>
-      <c r="L48" s="143"/>
-      <c r="M48" s="128"/>
-      <c r="N48" s="128"/>
-      <c r="O48" s="128"/>
-      <c r="P48" s="128"/>
-      <c r="Q48" s="128"/>
-      <c r="R48" s="128"/>
-      <c r="S48" s="133"/>
-      <c r="T48" s="134"/>
-    </row>
-    <row r="49" spans="2:20" ht="15" customHeight="1">
-      <c r="B49" s="9"/>
-      <c r="T49" s="10" t="s">
+      <c r="C47" s="215"/>
+      <c r="D47" s="216"/>
+      <c r="E47" s="232"/>
+      <c r="F47" s="233"/>
+      <c r="G47" s="233"/>
+      <c r="H47" s="234"/>
+      <c r="I47" s="232"/>
+      <c r="J47" s="234"/>
+      <c r="K47" s="232"/>
+      <c r="L47" s="234"/>
+      <c r="M47" s="221"/>
+      <c r="N47" s="221"/>
+      <c r="O47" s="221"/>
+      <c r="P47" s="221"/>
+      <c r="Q47" s="221"/>
+      <c r="R47" s="221"/>
+      <c r="S47" s="225"/>
+      <c r="T47" s="226"/>
+    </row>
+    <row r="48" ht="12" customHeight="1">
+      <c r="B48" s="111"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="235"/>
+      <c r="F48" s="236"/>
+      <c r="G48" s="236"/>
+      <c r="H48" s="237"/>
+      <c r="I48" s="235"/>
+      <c r="J48" s="237"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="237"/>
+      <c r="M48" s="222"/>
+      <c r="N48" s="222"/>
+      <c r="O48" s="222"/>
+      <c r="P48" s="222"/>
+      <c r="Q48" s="222"/>
+      <c r="R48" s="222"/>
+      <c r="S48" s="227"/>
+      <c r="T48" s="228"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="103"/>
+      <c r="T49" s="104" t="s">
         <v>39</v>
       </c>
     </row>
+    <row r="51">
+      <c r="K51" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="O51" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q51" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="S51" s="96" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells>
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="B30:G30"/>
     <mergeCell ref="B31:G31"/>
@@ -8634,7 +8732,8 @@
   <phoneticPr fontId="41"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8849,1072 +8948,1090 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:T49"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="0.85546875" style="2" customWidth="1"/>
-    <col min="2" max="20" width="4.28515625" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1" style="96"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1" style="96"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1" style="96"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1" style="96"/>
+    <col min="5" max="5" width="4.28515625" customWidth="1" style="96"/>
+    <col min="6" max="6" width="4.28515625" customWidth="1" style="96"/>
+    <col min="7" max="7" width="4.28515625" customWidth="1" style="96"/>
+    <col min="8" max="8" width="4.28515625" customWidth="1" style="96"/>
+    <col min="9" max="9" width="4.28515625" customWidth="1" style="96"/>
+    <col min="10" max="10" width="4.28515625" customWidth="1" style="96"/>
+    <col min="11" max="11" width="4.28515625" customWidth="1" style="96"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1" style="96"/>
+    <col min="13" max="13" width="4.28515625" customWidth="1" style="96"/>
+    <col min="14" max="14" width="4.28515625" customWidth="1" style="96"/>
+    <col min="15" max="15" width="4.28515625" customWidth="1" style="96"/>
+    <col min="16" max="16" width="4.28515625" customWidth="1" style="96"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1" style="96"/>
+    <col min="18" max="18" width="4.28515625" customWidth="1" style="96"/>
+    <col min="19" max="19" width="4.28515625" customWidth="1" style="96"/>
+    <col min="20" max="20" width="4.28515625" customWidth="1" style="96"/>
+    <col min="21" max="16384" width="9" customWidth="1" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20">
-      <c r="B1" s="1"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="2:20">
-      <c r="B2" s="4"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:20" ht="15.75" thickBot="1">
-      <c r="C3" s="5" t="s">
+    <row r="1">
+      <c r="B1" s="95"/>
+      <c r="G1" s="97"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="98"/>
+      <c r="G2" s="99"/>
+    </row>
+    <row r="3" ht="15.75">
+      <c r="C3" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="P3" s="22" t="s">
+      <c r="N3" s="97"/>
+      <c r="P3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="142"/>
-      <c r="R3" s="142"/>
-      <c r="S3" s="142"/>
-      <c r="T3" s="142"/>
-    </row>
-    <row r="4" spans="2:20" ht="18.75" customHeight="1">
-      <c r="B4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="56" t="s">
+      <c r="Q3" s="236"/>
+      <c r="R3" s="236"/>
+      <c r="S3" s="236"/>
+      <c r="T3" s="236"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="B4" s="147" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="148"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="148"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="57"/>
-      <c r="S4" s="56" t="s">
+      <c r="R4" s="151"/>
+      <c r="S4" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="59"/>
-    </row>
-    <row r="5" spans="2:20" ht="16.5" customHeight="1">
-      <c r="B5" s="182" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="183"/>
-      <c r="K5" s="183"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="183"/>
-      <c r="N5" s="183"/>
-      <c r="O5" s="183"/>
-      <c r="P5" s="184"/>
-      <c r="Q5" s="185" t="s">
+      <c r="T4" s="153"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="B5" s="276" t="s">
         <v>42</v>
       </c>
-      <c r="R5" s="186"/>
-      <c r="S5" s="185" t="s">
+      <c r="C5" s="277"/>
+      <c r="D5" s="277"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="277"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="277"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
+      <c r="L5" s="277"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="277"/>
+      <c r="O5" s="277"/>
+      <c r="P5" s="278"/>
+      <c r="Q5" s="279" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" s="280"/>
+      <c r="S5" s="279" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="187"/>
-    </row>
-    <row r="6" spans="2:20" ht="12" customHeight="1">
-      <c r="B6" s="67"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="188"/>
-      <c r="T6" s="78"/>
-    </row>
-    <row r="7" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B7" s="80" t="s">
+      <c r="T5" s="281"/>
+    </row>
+    <row r="6" ht="12" customHeight="1">
+      <c r="B6" s="161"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
+      <c r="Q6" s="166"/>
+      <c r="R6" s="167"/>
+      <c r="S6" s="282"/>
+      <c r="T6" s="172"/>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="B7" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="85" t="s">
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="177"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="177"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="189"/>
-      <c r="N7" s="189"/>
-      <c r="O7" s="189"/>
-      <c r="P7" s="190"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="188"/>
-      <c r="T7" s="78"/>
-    </row>
-    <row r="8" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B8" s="191" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="192"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="63" t="s">
+      <c r="L7" s="176"/>
+      <c r="M7" s="283"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="283"/>
+      <c r="P7" s="284"/>
+      <c r="Q7" s="166"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="282"/>
+      <c r="T7" s="172"/>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="B8" s="285" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="286"/>
+      <c r="D8" s="280"/>
+      <c r="E8" s="168"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="64"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="84"/>
-      <c r="T8" s="79"/>
-    </row>
-    <row r="9" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B9" s="80" t="s">
+      <c r="L8" s="158"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="169"/>
+      <c r="S8" s="178"/>
+      <c r="T8" s="173"/>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="B9" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="82"/>
-      <c r="M9" s="135"/>
-      <c r="N9" s="136"/>
-      <c r="O9" s="136"/>
-      <c r="P9" s="136"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="204"/>
-    </row>
-    <row r="10" spans="2:20" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B10" s="195" t="s">
+      <c r="C9" s="175"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="177"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="196"/>
-      <c r="D10" s="197"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="216" t="s">
+      <c r="L9" s="176"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="230"/>
+      <c r="O9" s="230"/>
+      <c r="P9" s="230"/>
+      <c r="Q9" s="230"/>
+      <c r="R9" s="230"/>
+      <c r="S9" s="230"/>
+      <c r="T9" s="298"/>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="B10" s="289" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="217"/>
-      <c r="M10" s="141"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="142"/>
-      <c r="P10" s="142"/>
-      <c r="Q10" s="142"/>
-      <c r="R10" s="142"/>
-      <c r="S10" s="142"/>
-      <c r="T10" s="205"/>
-    </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1">
-      <c r="B11" s="16" t="s">
+      <c r="C10" s="290"/>
+      <c r="D10" s="291"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="310" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52" t="s">
+      <c r="L10" s="311"/>
+      <c r="M10" s="235"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="236"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
+      <c r="T10" s="299"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="110" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="218"/>
-      <c r="S11" s="219"/>
-      <c r="T11" s="220"/>
-    </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1">
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="25"/>
-    </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1">
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="25"/>
-    </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1">
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="25"/>
-    </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1">
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="25"/>
-    </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1">
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="25"/>
-    </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1">
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="25"/>
-    </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1">
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="25"/>
-    </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="25"/>
-    </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1">
-      <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="25"/>
-    </row>
-    <row r="21" spans="2:20" ht="18" customHeight="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="25"/>
-    </row>
-    <row r="22" spans="2:20" ht="18" customHeight="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="25"/>
-    </row>
-    <row r="23" spans="2:20" ht="18" customHeight="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="25"/>
-    </row>
-    <row r="24" spans="2:20" ht="18" customHeight="1">
-      <c r="B24" s="23"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="25"/>
-    </row>
-    <row r="25" spans="2:20" ht="18" customHeight="1">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="28"/>
-    </row>
-    <row r="26" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B26" s="96" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
-      <c r="L26" s="97"/>
-      <c r="M26" s="97"/>
-      <c r="N26" s="97"/>
-      <c r="O26" s="97"/>
-      <c r="P26" s="97"/>
-      <c r="Q26" s="97"/>
-      <c r="R26" s="97"/>
-      <c r="S26" s="97"/>
-      <c r="T26" s="98"/>
-    </row>
-    <row r="27" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B27" s="221" t="s">
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="108"/>
+      <c r="Q11" s="109"/>
+      <c r="R11" s="312"/>
+      <c r="S11" s="313"/>
+      <c r="T11" s="314"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="119"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="117"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
+      <c r="T13" s="119"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="117"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="118"/>
+      <c r="T14" s="119"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="117"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="118"/>
+      <c r="T15" s="119"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="117"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="118"/>
+      <c r="T16" s="119"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="117"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="118"/>
+      <c r="P17" s="118"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="119"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="117"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="118"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="118"/>
+      <c r="T18" s="119"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="118"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="118"/>
+      <c r="T19" s="119"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="118"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="118"/>
+      <c r="T20" s="119"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="117"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="118"/>
+      <c r="S21" s="118"/>
+      <c r="T21" s="119"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="117"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="118"/>
+      <c r="Q22" s="118"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="118"/>
+      <c r="T22" s="119"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="118"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="118"/>
+      <c r="S23" s="118"/>
+      <c r="T23" s="119"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="117"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="118"/>
+      <c r="Q24" s="118"/>
+      <c r="R24" s="118"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="119"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="121"/>
+      <c r="R25" s="121"/>
+      <c r="S25" s="121"/>
+      <c r="T25" s="122"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="B26" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="222"/>
-      <c r="D27" s="222"/>
-      <c r="E27" s="222"/>
-      <c r="F27" s="222"/>
-      <c r="G27" s="222"/>
-      <c r="H27" s="222"/>
-      <c r="I27" s="222"/>
-      <c r="J27" s="222"/>
-      <c r="K27" s="222"/>
-      <c r="L27" s="222"/>
-      <c r="M27" s="222"/>
-      <c r="N27" s="222"/>
-      <c r="O27" s="222"/>
-      <c r="P27" s="222"/>
-      <c r="Q27" s="222"/>
-      <c r="R27" s="222"/>
-      <c r="S27" s="222"/>
-      <c r="T27" s="223"/>
-    </row>
-    <row r="28" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B28" s="172" t="s">
+      <c r="C26" s="191"/>
+      <c r="D26" s="191"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="191"/>
+      <c r="I26" s="191"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="191"/>
+      <c r="N26" s="191"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="191"/>
+      <c r="Q26" s="191"/>
+      <c r="R26" s="191"/>
+      <c r="S26" s="191"/>
+      <c r="T26" s="192"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="B27" s="315" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="316"/>
+      <c r="D27" s="316"/>
+      <c r="E27" s="316"/>
+      <c r="F27" s="316"/>
+      <c r="G27" s="316"/>
+      <c r="H27" s="316"/>
+      <c r="I27" s="316"/>
+      <c r="J27" s="316"/>
+      <c r="K27" s="316"/>
+      <c r="L27" s="316"/>
+      <c r="M27" s="316"/>
+      <c r="N27" s="316"/>
+      <c r="O27" s="316"/>
+      <c r="P27" s="316"/>
+      <c r="Q27" s="316"/>
+      <c r="R27" s="316"/>
+      <c r="S27" s="316"/>
+      <c r="T27" s="317"/>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="B28" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="173"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="173" t="s">
+      <c r="C28" s="267"/>
+      <c r="D28" s="267"/>
+      <c r="E28" s="267"/>
+      <c r="F28" s="267"/>
+      <c r="G28" s="267"/>
+      <c r="H28" s="267" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="173"/>
-      <c r="J28" s="173"/>
-      <c r="K28" s="173"/>
-      <c r="L28" s="173"/>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="173" t="s">
+      <c r="I28" s="267"/>
+      <c r="J28" s="267"/>
+      <c r="K28" s="267"/>
+      <c r="L28" s="267"/>
+      <c r="M28" s="267"/>
+      <c r="N28" s="267"/>
+      <c r="O28" s="267" t="s">
         <v>21</v>
       </c>
-      <c r="P28" s="173"/>
-      <c r="Q28" s="173"/>
-      <c r="R28" s="173"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="178"/>
-    </row>
-    <row r="29" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B29" s="193" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="194"/>
-      <c r="D29" s="194"/>
-      <c r="E29" s="194"/>
-      <c r="F29" s="194"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="194" t="s">
+      <c r="P28" s="267"/>
+      <c r="Q28" s="267"/>
+      <c r="R28" s="267"/>
+      <c r="S28" s="267"/>
+      <c r="T28" s="272"/>
+    </row>
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="B29" s="287" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="194"/>
-      <c r="J29" s="194"/>
-      <c r="K29" s="194"/>
-      <c r="L29" s="194"/>
-      <c r="M29" s="194"/>
-      <c r="N29" s="194"/>
-      <c r="O29" s="194" t="s">
+      <c r="C29" s="288"/>
+      <c r="D29" s="288"/>
+      <c r="E29" s="288"/>
+      <c r="F29" s="288"/>
+      <c r="G29" s="288"/>
+      <c r="H29" s="288" t="s">
         <v>52</v>
       </c>
-      <c r="P29" s="194"/>
-      <c r="Q29" s="194"/>
-      <c r="R29" s="194"/>
-      <c r="S29" s="194"/>
-      <c r="T29" s="226"/>
-    </row>
-    <row r="30" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B30" s="145" t="s">
+      <c r="I29" s="288"/>
+      <c r="J29" s="288"/>
+      <c r="K29" s="288"/>
+      <c r="L29" s="288"/>
+      <c r="M29" s="288"/>
+      <c r="N29" s="288"/>
+      <c r="O29" s="288" t="s">
+        <v>53</v>
+      </c>
+      <c r="P29" s="288"/>
+      <c r="Q29" s="288"/>
+      <c r="R29" s="288"/>
+      <c r="S29" s="288"/>
+      <c r="T29" s="320"/>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="B30" s="239" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="146"/>
-      <c r="D30" s="146"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="147"/>
-      <c r="H30" s="206"/>
-      <c r="I30" s="207"/>
-      <c r="J30" s="207"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
-      <c r="M30" s="207"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="207"/>
-      <c r="P30" s="207"/>
-      <c r="Q30" s="207"/>
-      <c r="R30" s="207"/>
-      <c r="S30" s="207"/>
-      <c r="T30" s="208"/>
-    </row>
-    <row r="31" spans="2:20" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B31" s="227" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="228"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="228"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="209"/>
-      <c r="I31" s="210"/>
-      <c r="J31" s="210"/>
-      <c r="K31" s="210"/>
-      <c r="L31" s="210"/>
-      <c r="M31" s="210"/>
-      <c r="N31" s="210"/>
-      <c r="O31" s="210"/>
-      <c r="P31" s="210"/>
-      <c r="Q31" s="210"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
-      <c r="T31" s="211"/>
-    </row>
-    <row r="32" spans="2:20" ht="6" customHeight="1" thickBot="1">
-      <c r="B32" s="6"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
-    </row>
-    <row r="33" spans="2:20" ht="18" customHeight="1">
-      <c r="B33" s="124" t="s">
+      <c r="C30" s="240"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="241"/>
+      <c r="H30" s="300"/>
+      <c r="I30" s="301"/>
+      <c r="J30" s="301"/>
+      <c r="K30" s="301"/>
+      <c r="L30" s="301"/>
+      <c r="M30" s="301"/>
+      <c r="N30" s="301"/>
+      <c r="O30" s="301"/>
+      <c r="P30" s="301"/>
+      <c r="Q30" s="301"/>
+      <c r="R30" s="301"/>
+      <c r="S30" s="301"/>
+      <c r="T30" s="302"/>
+    </row>
+    <row r="31" ht="13.5" customHeight="1">
+      <c r="B31" s="321" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="125"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="125"/>
-      <c r="R33" s="125"/>
-      <c r="S33" s="125"/>
-      <c r="T33" s="126"/>
-    </row>
-    <row r="34" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B34" s="201" t="s">
+      <c r="C31" s="322"/>
+      <c r="D31" s="322"/>
+      <c r="E31" s="322"/>
+      <c r="F31" s="322"/>
+      <c r="G31" s="323"/>
+      <c r="H31" s="303"/>
+      <c r="I31" s="304"/>
+      <c r="J31" s="304"/>
+      <c r="K31" s="304"/>
+      <c r="L31" s="304"/>
+      <c r="M31" s="304"/>
+      <c r="N31" s="304"/>
+      <c r="O31" s="304"/>
+      <c r="P31" s="304"/>
+      <c r="Q31" s="304"/>
+      <c r="R31" s="304"/>
+      <c r="S31" s="304"/>
+      <c r="T31" s="305"/>
+    </row>
+    <row r="32" ht="6" customHeight="1">
+      <c r="B32" s="100"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="107"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="107"/>
+      <c r="R32" s="107"/>
+      <c r="S32" s="107"/>
+      <c r="T32" s="107"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="218" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="202"/>
-      <c r="D34" s="202"/>
-      <c r="E34" s="202"/>
-      <c r="F34" s="202"/>
-      <c r="G34" s="202"/>
-      <c r="H34" s="202"/>
-      <c r="I34" s="202"/>
-      <c r="J34" s="202"/>
-      <c r="K34" s="202"/>
-      <c r="L34" s="202"/>
-      <c r="M34" s="202"/>
-      <c r="N34" s="202"/>
-      <c r="O34" s="202"/>
-      <c r="P34" s="202"/>
-      <c r="Q34" s="202"/>
-      <c r="R34" s="202"/>
-      <c r="S34" s="202"/>
-      <c r="T34" s="203"/>
-    </row>
-    <row r="35" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="25"/>
-    </row>
-    <row r="36" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="25"/>
-    </row>
-    <row r="37" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="25"/>
-    </row>
-    <row r="38" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="25"/>
-    </row>
-    <row r="39" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B39" s="35"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="36"/>
-      <c r="S39" s="36"/>
-      <c r="T39" s="37"/>
-    </row>
-    <row r="40" spans="2:20" ht="18" customHeight="1">
-      <c r="B40" s="38"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="39"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="40"/>
-    </row>
-    <row r="41" spans="2:20" ht="18" customHeight="1">
-      <c r="B41" s="38"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="40"/>
-    </row>
-    <row r="42" spans="2:20" ht="18" customHeight="1">
-      <c r="B42" s="38"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="39"/>
-      <c r="Q42" s="39"/>
-      <c r="R42" s="39"/>
-      <c r="S42" s="39"/>
-      <c r="T42" s="40"/>
-    </row>
-    <row r="43" spans="2:20" ht="18" customHeight="1">
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
-      <c r="K43" s="42"/>
-      <c r="L43" s="42"/>
-      <c r="M43" s="42"/>
-      <c r="N43" s="42"/>
-      <c r="O43" s="42"/>
-      <c r="P43" s="42"/>
-      <c r="Q43" s="42"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="42"/>
-      <c r="T43" s="43"/>
-    </row>
-    <row r="44" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B44" s="104" t="s">
+      <c r="C33" s="219"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="219"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="219"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="219"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="219"/>
+      <c r="Q33" s="219"/>
+      <c r="R33" s="219"/>
+      <c r="S33" s="219"/>
+      <c r="T33" s="220"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B34" s="295" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="296"/>
+      <c r="D34" s="296"/>
+      <c r="E34" s="296"/>
+      <c r="F34" s="296"/>
+      <c r="G34" s="296"/>
+      <c r="H34" s="296"/>
+      <c r="I34" s="296"/>
+      <c r="J34" s="296"/>
+      <c r="K34" s="296"/>
+      <c r="L34" s="296"/>
+      <c r="M34" s="296"/>
+      <c r="N34" s="296"/>
+      <c r="O34" s="296"/>
+      <c r="P34" s="296"/>
+      <c r="Q34" s="296"/>
+      <c r="R34" s="296"/>
+      <c r="S34" s="296"/>
+      <c r="T34" s="297"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B35" s="117"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="118"/>
+      <c r="M35" s="118"/>
+      <c r="N35" s="118"/>
+      <c r="O35" s="118"/>
+      <c r="P35" s="118"/>
+      <c r="Q35" s="118"/>
+      <c r="R35" s="118"/>
+      <c r="S35" s="118"/>
+      <c r="T35" s="119"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="118"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="118"/>
+      <c r="M36" s="118"/>
+      <c r="N36" s="118"/>
+      <c r="O36" s="118"/>
+      <c r="P36" s="118"/>
+      <c r="Q36" s="118"/>
+      <c r="R36" s="118"/>
+      <c r="S36" s="118"/>
+      <c r="T36" s="119"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B37" s="117"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="118"/>
+      <c r="M37" s="118"/>
+      <c r="N37" s="118"/>
+      <c r="O37" s="118"/>
+      <c r="P37" s="118"/>
+      <c r="Q37" s="118"/>
+      <c r="R37" s="118"/>
+      <c r="S37" s="118"/>
+      <c r="T37" s="119"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B38" s="117"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
+      <c r="M38" s="118"/>
+      <c r="N38" s="118"/>
+      <c r="O38" s="118"/>
+      <c r="P38" s="118"/>
+      <c r="Q38" s="118"/>
+      <c r="R38" s="118"/>
+      <c r="S38" s="118"/>
+      <c r="T38" s="119"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B39" s="129"/>
+      <c r="C39" s="130"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="130"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="130"/>
+      <c r="J39" s="130"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="130"/>
+      <c r="M39" s="130"/>
+      <c r="N39" s="130"/>
+      <c r="O39" s="130"/>
+      <c r="P39" s="130"/>
+      <c r="Q39" s="130"/>
+      <c r="R39" s="130"/>
+      <c r="S39" s="130"/>
+      <c r="T39" s="131"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="132"/>
+      <c r="C40" s="133"/>
+      <c r="D40" s="133"/>
+      <c r="E40" s="133"/>
+      <c r="F40" s="133"/>
+      <c r="G40" s="133"/>
+      <c r="H40" s="133"/>
+      <c r="I40" s="133"/>
+      <c r="J40" s="133"/>
+      <c r="K40" s="133"/>
+      <c r="L40" s="133"/>
+      <c r="M40" s="133"/>
+      <c r="N40" s="133"/>
+      <c r="O40" s="133"/>
+      <c r="P40" s="133"/>
+      <c r="Q40" s="133"/>
+      <c r="R40" s="133"/>
+      <c r="S40" s="133"/>
+      <c r="T40" s="134"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="132"/>
+      <c r="C41" s="133"/>
+      <c r="D41" s="133"/>
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="133"/>
+      <c r="I41" s="133"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="133"/>
+      <c r="M41" s="133"/>
+      <c r="N41" s="133"/>
+      <c r="O41" s="133"/>
+      <c r="P41" s="133"/>
+      <c r="Q41" s="133"/>
+      <c r="R41" s="133"/>
+      <c r="S41" s="133"/>
+      <c r="T41" s="134"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="132"/>
+      <c r="C42" s="133"/>
+      <c r="D42" s="133"/>
+      <c r="E42" s="133"/>
+      <c r="F42" s="133"/>
+      <c r="G42" s="133"/>
+      <c r="H42" s="133"/>
+      <c r="I42" s="133"/>
+      <c r="J42" s="133"/>
+      <c r="K42" s="133"/>
+      <c r="L42" s="133"/>
+      <c r="M42" s="133"/>
+      <c r="N42" s="133"/>
+      <c r="O42" s="133"/>
+      <c r="P42" s="133"/>
+      <c r="Q42" s="133"/>
+      <c r="R42" s="133"/>
+      <c r="S42" s="133"/>
+      <c r="T42" s="134"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="135"/>
+      <c r="C43" s="136"/>
+      <c r="D43" s="136"/>
+      <c r="E43" s="136"/>
+      <c r="F43" s="136"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="136"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="136"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
+      <c r="M43" s="136"/>
+      <c r="N43" s="136"/>
+      <c r="O43" s="136"/>
+      <c r="P43" s="136"/>
+      <c r="Q43" s="136"/>
+      <c r="R43" s="136"/>
+      <c r="S43" s="136"/>
+      <c r="T43" s="137"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1">
+      <c r="B44" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="105"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="12" t="s">
+      <c r="C44" s="199"/>
+      <c r="D44" s="200"/>
+      <c r="E44" s="106" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="107"/>
-      <c r="J44" s="107"/>
-      <c r="K44" s="108" t="s">
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="201"/>
+      <c r="J44" s="201"/>
+      <c r="K44" s="202" t="s">
         <v>31</v>
       </c>
-      <c r="L44" s="109"/>
-      <c r="M44" s="110" t="s">
+      <c r="L44" s="203"/>
+      <c r="M44" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="N44" s="103"/>
-      <c r="O44" s="110" t="s">
+      <c r="N44" s="197"/>
+      <c r="O44" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="P44" s="103"/>
-      <c r="Q44" s="110" t="s">
+      <c r="P44" s="197"/>
+      <c r="Q44" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="103"/>
-      <c r="S44" s="111" t="s">
+      <c r="R44" s="197"/>
+      <c r="S44" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="T44" s="112"/>
-    </row>
-    <row r="45" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B45" s="198" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" s="199"/>
-      <c r="D45" s="200"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
-      <c r="H45" s="119"/>
-      <c r="I45" s="123"/>
-      <c r="J45" s="123"/>
-      <c r="K45" s="224" t="s">
+      <c r="T44" s="206"/>
+    </row>
+    <row r="45" ht="13.5" customHeight="1">
+      <c r="B45" s="292" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="293"/>
+      <c r="D45" s="294"/>
+      <c r="E45" s="211"/>
+      <c r="F45" s="212"/>
+      <c r="G45" s="212"/>
+      <c r="H45" s="213"/>
+      <c r="I45" s="217"/>
+      <c r="J45" s="217"/>
+      <c r="K45" s="318" t="s">
         <v>57</v>
       </c>
-      <c r="L45" s="225"/>
-      <c r="M45" s="224" t="s">
+      <c r="L45" s="319"/>
+      <c r="M45" s="318" t="s">
         <v>58</v>
       </c>
-      <c r="N45" s="225"/>
-      <c r="O45" s="224" t="s">
+      <c r="N45" s="319"/>
+      <c r="O45" s="318" t="s">
         <v>58</v>
       </c>
-      <c r="P45" s="225"/>
-      <c r="Q45" s="224" t="s">
+      <c r="P45" s="319"/>
+      <c r="Q45" s="318" t="s">
         <v>4</v>
       </c>
-      <c r="R45" s="225"/>
-      <c r="S45" s="113"/>
-      <c r="T45" s="114"/>
-    </row>
-    <row r="46" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B46" s="104" t="s">
+      <c r="R45" s="319"/>
+      <c r="S45" s="207"/>
+      <c r="T45" s="208"/>
+    </row>
+    <row r="46" ht="13.5" customHeight="1">
+      <c r="B46" s="198" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="105"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="135"/>
-      <c r="F46" s="136"/>
-      <c r="G46" s="136"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="135"/>
-      <c r="J46" s="137"/>
-      <c r="K46" s="135"/>
-      <c r="L46" s="137"/>
-      <c r="M46" s="212"/>
-      <c r="N46" s="212"/>
-      <c r="O46" s="212"/>
-      <c r="P46" s="212"/>
-      <c r="Q46" s="212"/>
-      <c r="R46" s="212"/>
-      <c r="S46" s="212"/>
-      <c r="T46" s="213"/>
-    </row>
-    <row r="47" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B47" s="198" t="s">
+      <c r="C46" s="199"/>
+      <c r="D46" s="200"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="230"/>
+      <c r="G46" s="230"/>
+      <c r="H46" s="231"/>
+      <c r="I46" s="229"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="229"/>
+      <c r="L46" s="231"/>
+      <c r="M46" s="306"/>
+      <c r="N46" s="306"/>
+      <c r="O46" s="306"/>
+      <c r="P46" s="306"/>
+      <c r="Q46" s="306"/>
+      <c r="R46" s="306"/>
+      <c r="S46" s="306"/>
+      <c r="T46" s="307"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="B47" s="292" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="199"/>
-      <c r="D47" s="200"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="140"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="140"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="140"/>
-      <c r="M47" s="212"/>
-      <c r="N47" s="212"/>
-      <c r="O47" s="212"/>
-      <c r="P47" s="212"/>
-      <c r="Q47" s="212"/>
-      <c r="R47" s="212"/>
-      <c r="S47" s="212"/>
-      <c r="T47" s="213"/>
-    </row>
-    <row r="48" spans="2:20" ht="12" customHeight="1" thickBot="1">
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="141"/>
-      <c r="J48" s="143"/>
-      <c r="K48" s="141"/>
-      <c r="L48" s="143"/>
-      <c r="M48" s="214"/>
-      <c r="N48" s="214"/>
-      <c r="O48" s="214"/>
-      <c r="P48" s="214"/>
-      <c r="Q48" s="214"/>
-      <c r="R48" s="214"/>
-      <c r="S48" s="214"/>
-      <c r="T48" s="215"/>
-    </row>
-    <row r="49" spans="2:20" ht="15" customHeight="1">
-      <c r="B49" s="9"/>
-      <c r="T49" s="10" t="s">
+      <c r="C47" s="293"/>
+      <c r="D47" s="294"/>
+      <c r="E47" s="232"/>
+      <c r="F47" s="233"/>
+      <c r="G47" s="233"/>
+      <c r="H47" s="234"/>
+      <c r="I47" s="232"/>
+      <c r="J47" s="234"/>
+      <c r="K47" s="232"/>
+      <c r="L47" s="234"/>
+      <c r="M47" s="306"/>
+      <c r="N47" s="306"/>
+      <c r="O47" s="306"/>
+      <c r="P47" s="306"/>
+      <c r="Q47" s="306"/>
+      <c r="R47" s="306"/>
+      <c r="S47" s="306"/>
+      <c r="T47" s="307"/>
+    </row>
+    <row r="48" ht="12" customHeight="1">
+      <c r="B48" s="111"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="235"/>
+      <c r="F48" s="236"/>
+      <c r="G48" s="236"/>
+      <c r="H48" s="237"/>
+      <c r="I48" s="235"/>
+      <c r="J48" s="237"/>
+      <c r="K48" s="235"/>
+      <c r="L48" s="237"/>
+      <c r="M48" s="308"/>
+      <c r="N48" s="308"/>
+      <c r="O48" s="308"/>
+      <c r="P48" s="308"/>
+      <c r="Q48" s="308"/>
+      <c r="R48" s="308"/>
+      <c r="S48" s="308"/>
+      <c r="T48" s="309"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="103"/>
+      <c r="T49" s="104" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells>
     <mergeCell ref="K46:L48"/>
     <mergeCell ref="M46:N48"/>
     <mergeCell ref="O29:T29"/>
@@ -9978,7 +10095,8 @@
   <phoneticPr fontId="41"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10193,1072 +10311,1090 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:T49"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="0.85546875" style="2" customWidth="1"/>
-    <col min="2" max="20" width="4.28515625" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1" style="96"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1" style="96"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1" style="96"/>
+    <col min="4" max="4" width="4.28515625" customWidth="1" style="96"/>
+    <col min="5" max="5" width="4.28515625" customWidth="1" style="96"/>
+    <col min="6" max="6" width="4.28515625" customWidth="1" style="96"/>
+    <col min="7" max="7" width="4.28515625" customWidth="1" style="96"/>
+    <col min="8" max="8" width="4.28515625" customWidth="1" style="96"/>
+    <col min="9" max="9" width="4.28515625" customWidth="1" style="96"/>
+    <col min="10" max="10" width="4.28515625" customWidth="1" style="96"/>
+    <col min="11" max="11" width="4.28515625" customWidth="1" style="96"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1" style="96"/>
+    <col min="13" max="13" width="4.28515625" customWidth="1" style="96"/>
+    <col min="14" max="14" width="4.28515625" customWidth="1" style="96"/>
+    <col min="15" max="15" width="4.28515625" customWidth="1" style="96"/>
+    <col min="16" max="16" width="4.28515625" customWidth="1" style="96"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1" style="96"/>
+    <col min="18" max="18" width="4.28515625" customWidth="1" style="96"/>
+    <col min="19" max="19" width="4.28515625" customWidth="1" style="96"/>
+    <col min="20" max="20" width="4.28515625" customWidth="1" style="96"/>
+    <col min="21" max="16384" width="9" customWidth="1" style="96"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20">
-      <c r="B1" s="1"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="2:20">
-      <c r="B2" s="4"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:20" ht="15.75" thickBot="1">
-      <c r="C3" s="5" t="s">
+    <row r="1">
+      <c r="B1" s="95"/>
+      <c r="G1" s="97"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="98"/>
+      <c r="G2" s="99"/>
+    </row>
+    <row r="3" ht="15.75">
+      <c r="C3" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="P3" s="22" t="s">
+      <c r="N3" s="97"/>
+      <c r="P3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="144"/>
-      <c r="R3" s="144"/>
-      <c r="S3" s="144"/>
-      <c r="T3" s="144"/>
-    </row>
-    <row r="4" spans="2:20" ht="18.75" customHeight="1">
-      <c r="B4" s="53" t="s">
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="238"/>
+      <c r="T3" s="238"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="B4" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="56" t="s">
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="148"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="148"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="57"/>
-      <c r="S4" s="58" t="s">
+      <c r="R4" s="151"/>
+      <c r="S4" s="152" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="59"/>
-    </row>
-    <row r="5" spans="2:20" ht="16.5" customHeight="1">
-      <c r="B5" s="60" t="s">
+      <c r="T4" s="153"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="B5" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="230" t="s">
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="156"/>
+      <c r="Q5" s="324" t="s">
         <v>61</v>
       </c>
-      <c r="R5" s="231"/>
-      <c r="S5" s="232" t="s">
+      <c r="R5" s="325"/>
+      <c r="S5" s="326" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="233"/>
-    </row>
-    <row r="6" spans="2:20" ht="12" customHeight="1">
-      <c r="B6" s="67"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="188"/>
-      <c r="T6" s="78"/>
-    </row>
-    <row r="7" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B7" s="80" t="s">
+      <c r="T5" s="327"/>
+    </row>
+    <row r="6" ht="12" customHeight="1">
+      <c r="B6" s="161"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+      <c r="K6" s="162"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="162"/>
+      <c r="N6" s="162"/>
+      <c r="O6" s="162"/>
+      <c r="P6" s="163"/>
+      <c r="Q6" s="166"/>
+      <c r="R6" s="167"/>
+      <c r="S6" s="282"/>
+      <c r="T6" s="172"/>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="B7" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="85" t="s">
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="177"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="177"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="189"/>
-      <c r="N7" s="189"/>
-      <c r="O7" s="189"/>
-      <c r="P7" s="190"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="188"/>
-      <c r="T7" s="78"/>
-    </row>
-    <row r="8" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B8" s="92" t="s">
+      <c r="L7" s="176"/>
+      <c r="M7" s="283"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="283"/>
+      <c r="P7" s="284"/>
+      <c r="Q7" s="166"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="282"/>
+      <c r="T7" s="172"/>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="B8" s="186" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="63" t="s">
+      <c r="C8" s="159"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="168"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="64"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="84"/>
-      <c r="T8" s="79"/>
-    </row>
-    <row r="9" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B9" s="80" t="s">
+      <c r="L8" s="158"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="169"/>
+      <c r="S8" s="178"/>
+      <c r="T8" s="173"/>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="B9" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="82"/>
-      <c r="M9" s="160"/>
-      <c r="N9" s="161"/>
-      <c r="O9" s="161"/>
-      <c r="P9" s="161"/>
-      <c r="Q9" s="161"/>
-      <c r="R9" s="161"/>
-      <c r="S9" s="161"/>
-      <c r="T9" s="162"/>
-    </row>
-    <row r="10" spans="2:20" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B10" s="93" t="s">
+      <c r="C9" s="175"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="177"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="179" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="176"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="255"/>
+      <c r="O9" s="255"/>
+      <c r="P9" s="255"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="256"/>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="B10" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="238" t="s">
+      <c r="C10" s="188"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="332" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="239"/>
-      <c r="M10" s="163"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
-      <c r="P10" s="164"/>
-      <c r="Q10" s="164"/>
-      <c r="R10" s="164"/>
-      <c r="S10" s="164"/>
-      <c r="T10" s="165"/>
-    </row>
-    <row r="11" spans="2:20" ht="18" customHeight="1">
-      <c r="B11" s="16" t="s">
+      <c r="L10" s="333"/>
+      <c r="M10" s="257"/>
+      <c r="N10" s="258"/>
+      <c r="O10" s="258"/>
+      <c r="P10" s="258"/>
+      <c r="Q10" s="258"/>
+      <c r="R10" s="258"/>
+      <c r="S10" s="258"/>
+      <c r="T10" s="259"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="151" t="s">
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
+      <c r="M11" s="245" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="152"/>
-      <c r="O11" s="152"/>
-      <c r="P11" s="152"/>
-      <c r="Q11" s="153"/>
-      <c r="R11" s="218"/>
-      <c r="S11" s="219"/>
-      <c r="T11" s="220"/>
-    </row>
-    <row r="12" spans="2:20" ht="18" customHeight="1">
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="25"/>
-    </row>
-    <row r="13" spans="2:20" ht="18" customHeight="1">
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="25"/>
-    </row>
-    <row r="14" spans="2:20" ht="18" customHeight="1">
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="25"/>
-    </row>
-    <row r="15" spans="2:20" ht="18" customHeight="1">
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="25"/>
-    </row>
-    <row r="16" spans="2:20" ht="18" customHeight="1">
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="25"/>
-    </row>
-    <row r="17" spans="2:20" ht="18" customHeight="1">
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="25"/>
-    </row>
-    <row r="18" spans="2:20" ht="18" customHeight="1">
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="25"/>
-    </row>
-    <row r="19" spans="2:20" ht="18" customHeight="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="25"/>
-    </row>
-    <row r="20" spans="2:20" ht="18" customHeight="1">
-      <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="25"/>
-    </row>
-    <row r="21" spans="2:20" ht="18" customHeight="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="25"/>
-    </row>
-    <row r="22" spans="2:20" ht="18" customHeight="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="25"/>
-    </row>
-    <row r="23" spans="2:20" ht="18" customHeight="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="25"/>
-    </row>
-    <row r="24" spans="2:20" ht="18" customHeight="1">
-      <c r="B24" s="23"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="25"/>
-    </row>
-    <row r="25" spans="2:20" ht="18" customHeight="1">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="28"/>
-    </row>
-    <row r="26" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B26" s="96" t="s">
+      <c r="N11" s="246"/>
+      <c r="O11" s="246"/>
+      <c r="P11" s="246"/>
+      <c r="Q11" s="247"/>
+      <c r="R11" s="312"/>
+      <c r="S11" s="313"/>
+      <c r="T11" s="314"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="119"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="117"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
+      <c r="T13" s="119"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="117"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="118"/>
+      <c r="T14" s="119"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="117"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="118"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="118"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="118"/>
+      <c r="P15" s="118"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="118"/>
+      <c r="T15" s="119"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="117"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="118"/>
+      <c r="T16" s="119"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="117"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
+      <c r="O17" s="118"/>
+      <c r="P17" s="118"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="118"/>
+      <c r="T17" s="119"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="117"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="118"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="118"/>
+      <c r="T18" s="119"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="118"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="118"/>
+      <c r="T19" s="119"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="118"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="118"/>
+      <c r="T20" s="119"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="117"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="118"/>
+      <c r="S21" s="118"/>
+      <c r="T21" s="119"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="117"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="118"/>
+      <c r="Q22" s="118"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="118"/>
+      <c r="T22" s="119"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="118"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="118"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="118"/>
+      <c r="S23" s="118"/>
+      <c r="T23" s="119"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="117"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="118"/>
+      <c r="Q24" s="118"/>
+      <c r="R24" s="118"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="119"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="121"/>
+      <c r="R25" s="121"/>
+      <c r="S25" s="121"/>
+      <c r="T25" s="122"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="B26" s="190" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
-      <c r="L26" s="97"/>
-      <c r="M26" s="97"/>
-      <c r="N26" s="97"/>
-      <c r="O26" s="97"/>
-      <c r="P26" s="97"/>
-      <c r="Q26" s="97"/>
-      <c r="R26" s="97"/>
-      <c r="S26" s="97"/>
-      <c r="T26" s="98"/>
-    </row>
-    <row r="27" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B27" s="99" t="s">
+      <c r="C26" s="191"/>
+      <c r="D26" s="191"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="191"/>
+      <c r="I26" s="191"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="191"/>
+      <c r="N26" s="191"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="191"/>
+      <c r="Q26" s="191"/>
+      <c r="R26" s="191"/>
+      <c r="S26" s="191"/>
+      <c r="T26" s="192"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="B27" s="193" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="100"/>
-      <c r="N27" s="100"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="100"/>
-      <c r="Q27" s="100"/>
-      <c r="R27" s="100"/>
-      <c r="S27" s="100"/>
-      <c r="T27" s="101"/>
-    </row>
-    <row r="28" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B28" s="172" t="s">
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="194"/>
+      <c r="L27" s="194"/>
+      <c r="M27" s="194"/>
+      <c r="N27" s="194"/>
+      <c r="O27" s="194"/>
+      <c r="P27" s="194"/>
+      <c r="Q27" s="194"/>
+      <c r="R27" s="194"/>
+      <c r="S27" s="194"/>
+      <c r="T27" s="195"/>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="B28" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="173"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="173" t="s">
+      <c r="C28" s="267"/>
+      <c r="D28" s="267"/>
+      <c r="E28" s="267"/>
+      <c r="F28" s="267"/>
+      <c r="G28" s="267"/>
+      <c r="H28" s="267" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="173"/>
-      <c r="J28" s="173"/>
-      <c r="K28" s="173"/>
-      <c r="L28" s="173"/>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="173" t="s">
+      <c r="I28" s="267"/>
+      <c r="J28" s="267"/>
+      <c r="K28" s="267"/>
+      <c r="L28" s="267"/>
+      <c r="M28" s="267"/>
+      <c r="N28" s="267"/>
+      <c r="O28" s="267" t="s">
         <v>21</v>
       </c>
-      <c r="P28" s="173"/>
-      <c r="Q28" s="173"/>
-      <c r="R28" s="173"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="178"/>
-    </row>
-    <row r="29" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B29" s="234" t="s">
+      <c r="P28" s="267"/>
+      <c r="Q28" s="267"/>
+      <c r="R28" s="267"/>
+      <c r="S28" s="267"/>
+      <c r="T28" s="272"/>
+    </row>
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="B29" s="328" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="177"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="177"/>
-      <c r="F29" s="177"/>
-      <c r="G29" s="177"/>
-      <c r="H29" s="177" t="s">
+      <c r="C29" s="271"/>
+      <c r="D29" s="271"/>
+      <c r="E29" s="271"/>
+      <c r="F29" s="271"/>
+      <c r="G29" s="271"/>
+      <c r="H29" s="271" t="s">
         <v>70</v>
       </c>
-      <c r="I29" s="177"/>
-      <c r="J29" s="177"/>
-      <c r="K29" s="177"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="177"/>
-      <c r="N29" s="177"/>
-      <c r="O29" s="177" t="s">
+      <c r="I29" s="271"/>
+      <c r="J29" s="271"/>
+      <c r="K29" s="271"/>
+      <c r="L29" s="271"/>
+      <c r="M29" s="271"/>
+      <c r="N29" s="271"/>
+      <c r="O29" s="271" t="s">
         <v>71</v>
       </c>
-      <c r="P29" s="177"/>
-      <c r="Q29" s="177"/>
-      <c r="R29" s="177"/>
-      <c r="S29" s="177"/>
-      <c r="T29" s="179"/>
-    </row>
-    <row r="30" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B30" s="145" t="s">
+      <c r="P29" s="271"/>
+      <c r="Q29" s="271"/>
+      <c r="R29" s="271"/>
+      <c r="S29" s="271"/>
+      <c r="T29" s="273"/>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="B30" s="239" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="146"/>
-      <c r="D30" s="146"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="147"/>
-      <c r="H30" s="240"/>
-      <c r="I30" s="241"/>
-      <c r="J30" s="241"/>
-      <c r="K30" s="241"/>
-      <c r="L30" s="241"/>
-      <c r="M30" s="241"/>
-      <c r="N30" s="241"/>
-      <c r="O30" s="241"/>
-      <c r="P30" s="241"/>
-      <c r="Q30" s="241"/>
-      <c r="R30" s="241"/>
-      <c r="S30" s="241"/>
-      <c r="T30" s="242"/>
-    </row>
-    <row r="31" spans="2:20" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B31" s="148" t="s">
+      <c r="C30" s="240"/>
+      <c r="D30" s="240"/>
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="241"/>
+      <c r="H30" s="334"/>
+      <c r="I30" s="335"/>
+      <c r="J30" s="335"/>
+      <c r="K30" s="335"/>
+      <c r="L30" s="335"/>
+      <c r="M30" s="335"/>
+      <c r="N30" s="335"/>
+      <c r="O30" s="335"/>
+      <c r="P30" s="335"/>
+      <c r="Q30" s="335"/>
+      <c r="R30" s="335"/>
+      <c r="S30" s="335"/>
+      <c r="T30" s="336"/>
+    </row>
+    <row r="31" ht="13.5" customHeight="1">
+      <c r="B31" s="242" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="149"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="150"/>
-      <c r="H31" s="243"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
-      <c r="M31" s="244"/>
-      <c r="N31" s="244"/>
-      <c r="O31" s="244"/>
-      <c r="P31" s="244"/>
-      <c r="Q31" s="244"/>
-      <c r="R31" s="244"/>
-      <c r="S31" s="244"/>
-      <c r="T31" s="245"/>
-    </row>
-    <row r="32" spans="2:20" ht="6" customHeight="1" thickBot="1">
-      <c r="B32" s="6"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
-    </row>
-    <row r="33" spans="2:20" ht="18" customHeight="1">
-      <c r="B33" s="124" t="s">
+      <c r="C31" s="243"/>
+      <c r="D31" s="243"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="337"/>
+      <c r="I31" s="338"/>
+      <c r="J31" s="338"/>
+      <c r="K31" s="338"/>
+      <c r="L31" s="338"/>
+      <c r="M31" s="338"/>
+      <c r="N31" s="338"/>
+      <c r="O31" s="338"/>
+      <c r="P31" s="338"/>
+      <c r="Q31" s="338"/>
+      <c r="R31" s="338"/>
+      <c r="S31" s="338"/>
+      <c r="T31" s="339"/>
+    </row>
+    <row r="32" ht="6" customHeight="1">
+      <c r="B32" s="100"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="107"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="107"/>
+      <c r="R32" s="107"/>
+      <c r="S32" s="107"/>
+      <c r="T32" s="107"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="218" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="125"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="125"/>
-      <c r="R33" s="125"/>
-      <c r="S33" s="125"/>
-      <c r="T33" s="126"/>
-    </row>
-    <row r="34" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B34" s="115" t="s">
+      <c r="C33" s="219"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="219"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="219"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="219"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="219"/>
+      <c r="Q33" s="219"/>
+      <c r="R33" s="219"/>
+      <c r="S33" s="219"/>
+      <c r="T33" s="220"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B34" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="116"/>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="21"/>
-    </row>
-    <row r="35" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="24"/>
-      <c r="T35" s="25"/>
-    </row>
-    <row r="36" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="25"/>
-    </row>
-    <row r="37" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="24"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="25"/>
-    </row>
-    <row r="38" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="25"/>
-    </row>
-    <row r="39" spans="2:20" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="24"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="24"/>
-      <c r="T39" s="25"/>
-    </row>
-    <row r="40" spans="2:20" ht="18" customHeight="1">
-      <c r="B40" s="23"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="25"/>
-    </row>
-    <row r="41" spans="2:20" ht="18" customHeight="1">
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="24"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="24"/>
-      <c r="T41" s="25"/>
-    </row>
-    <row r="42" spans="2:20" ht="18" customHeight="1">
-      <c r="B42" s="23"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24"/>
-      <c r="N42" s="24"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="24"/>
-      <c r="Q42" s="24"/>
-      <c r="R42" s="24"/>
-      <c r="S42" s="24"/>
-      <c r="T42" s="25"/>
-    </row>
-    <row r="43" spans="2:20" ht="18" customHeight="1">
-      <c r="B43" s="26"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="28"/>
-    </row>
-    <row r="44" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B44" s="104" t="s">
+      <c r="C34" s="210"/>
+      <c r="D34" s="210"/>
+      <c r="E34" s="210"/>
+      <c r="F34" s="210"/>
+      <c r="G34" s="210"/>
+      <c r="H34" s="210"/>
+      <c r="I34" s="210"/>
+      <c r="J34" s="210"/>
+      <c r="K34" s="210"/>
+      <c r="L34" s="114"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="114"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="114"/>
+      <c r="Q34" s="114"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="114"/>
+      <c r="T34" s="115"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B35" s="117"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="118"/>
+      <c r="M35" s="118"/>
+      <c r="N35" s="118"/>
+      <c r="O35" s="118"/>
+      <c r="P35" s="118"/>
+      <c r="Q35" s="118"/>
+      <c r="R35" s="118"/>
+      <c r="S35" s="118"/>
+      <c r="T35" s="119"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B36" s="117"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="118"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="118"/>
+      <c r="M36" s="118"/>
+      <c r="N36" s="118"/>
+      <c r="O36" s="118"/>
+      <c r="P36" s="118"/>
+      <c r="Q36" s="118"/>
+      <c r="R36" s="118"/>
+      <c r="S36" s="118"/>
+      <c r="T36" s="119"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B37" s="117"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="118"/>
+      <c r="M37" s="118"/>
+      <c r="N37" s="118"/>
+      <c r="O37" s="118"/>
+      <c r="P37" s="118"/>
+      <c r="Q37" s="118"/>
+      <c r="R37" s="118"/>
+      <c r="S37" s="118"/>
+      <c r="T37" s="119"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B38" s="117"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
+      <c r="M38" s="118"/>
+      <c r="N38" s="118"/>
+      <c r="O38" s="118"/>
+      <c r="P38" s="118"/>
+      <c r="Q38" s="118"/>
+      <c r="R38" s="118"/>
+      <c r="S38" s="118"/>
+      <c r="T38" s="119"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="102" customFormat="1">
+      <c r="B39" s="117"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="118"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
+      <c r="M39" s="118"/>
+      <c r="N39" s="118"/>
+      <c r="O39" s="118"/>
+      <c r="P39" s="118"/>
+      <c r="Q39" s="118"/>
+      <c r="R39" s="118"/>
+      <c r="S39" s="118"/>
+      <c r="T39" s="119"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="117"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="118"/>
+      <c r="N40" s="118"/>
+      <c r="O40" s="118"/>
+      <c r="P40" s="118"/>
+      <c r="Q40" s="118"/>
+      <c r="R40" s="118"/>
+      <c r="S40" s="118"/>
+      <c r="T40" s="119"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="117"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
+      <c r="M41" s="118"/>
+      <c r="N41" s="118"/>
+      <c r="O41" s="118"/>
+      <c r="P41" s="118"/>
+      <c r="Q41" s="118"/>
+      <c r="R41" s="118"/>
+      <c r="S41" s="118"/>
+      <c r="T41" s="119"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="117"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="118"/>
+      <c r="M42" s="118"/>
+      <c r="N42" s="118"/>
+      <c r="O42" s="118"/>
+      <c r="P42" s="118"/>
+      <c r="Q42" s="118"/>
+      <c r="R42" s="118"/>
+      <c r="S42" s="118"/>
+      <c r="T42" s="119"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="120"/>
+      <c r="C43" s="121"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="121"/>
+      <c r="H43" s="121"/>
+      <c r="I43" s="121"/>
+      <c r="J43" s="121"/>
+      <c r="K43" s="121"/>
+      <c r="L43" s="121"/>
+      <c r="M43" s="121"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="121"/>
+      <c r="R43" s="121"/>
+      <c r="S43" s="121"/>
+      <c r="T43" s="122"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1">
+      <c r="B44" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="105"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="12" t="s">
+      <c r="C44" s="199"/>
+      <c r="D44" s="200"/>
+      <c r="E44" s="106" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="237"/>
-      <c r="J44" s="237"/>
-      <c r="K44" s="108" t="s">
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="331"/>
+      <c r="J44" s="331"/>
+      <c r="K44" s="202" t="s">
         <v>31</v>
       </c>
-      <c r="L44" s="109"/>
-      <c r="M44" s="110" t="s">
+      <c r="L44" s="203"/>
+      <c r="M44" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="N44" s="103"/>
-      <c r="O44" s="110" t="s">
+      <c r="N44" s="197"/>
+      <c r="O44" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="P44" s="103"/>
-      <c r="Q44" s="110" t="s">
+      <c r="P44" s="197"/>
+      <c r="Q44" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="103"/>
-      <c r="S44" s="111" t="s">
+      <c r="R44" s="197"/>
+      <c r="S44" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="T44" s="112"/>
-    </row>
-    <row r="45" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B45" s="120" t="s">
+      <c r="T44" s="206"/>
+    </row>
+    <row r="45" ht="13.5" customHeight="1">
+      <c r="B45" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="D45" s="236"/>
-      <c r="E45" s="117"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="118"/>
-      <c r="H45" s="119"/>
-      <c r="I45" s="237"/>
-      <c r="J45" s="237"/>
-      <c r="K45" s="102" t="s">
+      <c r="C45" s="329"/>
+      <c r="D45" s="330"/>
+      <c r="E45" s="211"/>
+      <c r="F45" s="212"/>
+      <c r="G45" s="212"/>
+      <c r="H45" s="213"/>
+      <c r="I45" s="331"/>
+      <c r="J45" s="331"/>
+      <c r="K45" s="196" t="s">
         <v>76</v>
       </c>
-      <c r="L45" s="103"/>
-      <c r="M45" s="102" t="s">
+      <c r="L45" s="197"/>
+      <c r="M45" s="196" t="s">
         <v>77</v>
       </c>
-      <c r="N45" s="103"/>
-      <c r="O45" s="102" t="s">
+      <c r="N45" s="197"/>
+      <c r="O45" s="196" t="s">
         <v>77</v>
       </c>
-      <c r="P45" s="103"/>
-      <c r="Q45" s="102" t="s">
+      <c r="P45" s="197"/>
+      <c r="Q45" s="196" t="s">
         <v>62</v>
       </c>
-      <c r="R45" s="103"/>
-      <c r="S45" s="113"/>
-      <c r="T45" s="114"/>
-    </row>
-    <row r="46" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B46" s="104" t="s">
+      <c r="R45" s="197"/>
+      <c r="S45" s="207"/>
+      <c r="T45" s="208"/>
+    </row>
+    <row r="46" ht="13.5" customHeight="1">
+      <c r="B46" s="198" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="105"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="135"/>
-      <c r="F46" s="136"/>
-      <c r="G46" s="136"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="135"/>
-      <c r="J46" s="137"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="212"/>
-      <c r="N46" s="212"/>
-      <c r="O46" s="212"/>
-      <c r="P46" s="212"/>
-      <c r="Q46" s="212"/>
-      <c r="R46" s="212"/>
-      <c r="S46" s="212"/>
-      <c r="T46" s="213"/>
-    </row>
-    <row r="47" spans="2:20" ht="13.5" customHeight="1">
-      <c r="B47" s="120" t="s">
+      <c r="C46" s="199"/>
+      <c r="D46" s="200"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="230"/>
+      <c r="G46" s="230"/>
+      <c r="H46" s="231"/>
+      <c r="I46" s="229"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="139"/>
+      <c r="L46" s="140"/>
+      <c r="M46" s="306"/>
+      <c r="N46" s="306"/>
+      <c r="O46" s="306"/>
+      <c r="P46" s="306"/>
+      <c r="Q46" s="306"/>
+      <c r="R46" s="306"/>
+      <c r="S46" s="306"/>
+      <c r="T46" s="307"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="B47" s="214" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="235"/>
-      <c r="D47" s="236"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="140"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="140"/>
-      <c r="K47" s="47"/>
-      <c r="L47" s="48"/>
-      <c r="M47" s="212"/>
-      <c r="N47" s="212"/>
-      <c r="O47" s="212"/>
-      <c r="P47" s="212"/>
-      <c r="Q47" s="212"/>
-      <c r="R47" s="212"/>
-      <c r="S47" s="212"/>
-      <c r="T47" s="213"/>
-    </row>
-    <row r="48" spans="2:20" ht="12" customHeight="1" thickBot="1">
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="143"/>
-      <c r="I48" s="141"/>
-      <c r="J48" s="143"/>
-      <c r="K48" s="49"/>
-      <c r="L48" s="50"/>
-      <c r="M48" s="214"/>
-      <c r="N48" s="214"/>
-      <c r="O48" s="214"/>
-      <c r="P48" s="214"/>
-      <c r="Q48" s="214"/>
-      <c r="R48" s="214"/>
-      <c r="S48" s="214"/>
-      <c r="T48" s="215"/>
-    </row>
-    <row r="49" spans="2:20" ht="15" customHeight="1">
-      <c r="B49" s="9"/>
-      <c r="T49" s="10" t="s">
+      <c r="C47" s="329"/>
+      <c r="D47" s="330"/>
+      <c r="E47" s="232"/>
+      <c r="F47" s="233"/>
+      <c r="G47" s="233"/>
+      <c r="H47" s="234"/>
+      <c r="I47" s="232"/>
+      <c r="J47" s="234"/>
+      <c r="K47" s="141"/>
+      <c r="L47" s="142"/>
+      <c r="M47" s="306"/>
+      <c r="N47" s="306"/>
+      <c r="O47" s="306"/>
+      <c r="P47" s="306"/>
+      <c r="Q47" s="306"/>
+      <c r="R47" s="306"/>
+      <c r="S47" s="306"/>
+      <c r="T47" s="307"/>
+    </row>
+    <row r="48" ht="12" customHeight="1">
+      <c r="B48" s="111"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="235"/>
+      <c r="F48" s="236"/>
+      <c r="G48" s="236"/>
+      <c r="H48" s="237"/>
+      <c r="I48" s="235"/>
+      <c r="J48" s="237"/>
+      <c r="K48" s="143"/>
+      <c r="L48" s="144"/>
+      <c r="M48" s="308"/>
+      <c r="N48" s="308"/>
+      <c r="O48" s="308"/>
+      <c r="P48" s="308"/>
+      <c r="Q48" s="308"/>
+      <c r="R48" s="308"/>
+      <c r="S48" s="308"/>
+      <c r="T48" s="309"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="103"/>
+      <c r="T49" s="104" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells>
     <mergeCell ref="S46:T48"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="K9:L9"/>
@@ -11322,7 +11458,8 @@
   <phoneticPr fontId="41"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
